--- a/_ JV攻略マイルストーン ワークシート.xlsx
+++ b/_ JV攻略マイルストーン ワークシート.xlsx
@@ -4703,10 +4703,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B8:B13"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B5:B7"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B8:B13"/>
-    <mergeCell ref="B5:B7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5178,7 +5178,7 @@
       </c>
       <c r="D13" s="127" t="n"/>
     </row>
-    <row r="14" ht="470" customHeight="1" s="272">
+    <row r="14" ht="520" customHeight="1" s="272">
       <c r="A14" s="127" t="n"/>
       <c r="B14" s="138" t="inlineStr">
         <is>
@@ -5199,9 +5199,10 @@
 　② 自分のリスト（メルマガ約300人）だけでは売上の桁が変わらない。
 　　　コミュニティの講師という立場は、認知・信頼・集客を制度的に一度に得られる。
 　　　note講師の席も空いている。取りに行かない理由がない。
-　③ 主催者から道を示唆していただいた。
+　③ 主催者から道を示唆していただき、「月50万は全然いける」とも言っていただいた。
 　　　これは「ギブをしよう」という気持ちから出たものだと受け止めている。
-　　　その想いに応えたい。だから今は自分の売上を追わず、運営に返すことを最優先にする。
+　　　その言葉を信じ、その想いに応えたい。
+　　　だから今は自分の売上を追わず、運営に返すことを最優先にする。
 【当面のスタンス】
 　運営にフルコミットする。自分の売上は追わない。
 　運営が求めているのは「ゼロイチ達成の支援」と「講座の確立」。この2つに一点集中する。
@@ -5215,7 +5216,9 @@
 【既存ゼロイチ講師との関係】
 　競合しない。note媒体特化 × AI自動化 × 労力最小という手段特化で、後工程に立つ。
 【短期売上について】
-　二の次。ただしモニター募集は運営へのギブと同一行動のため、結果として付いてくる。</t>
+　二の次。ただしモニター募集は運営へのギブと同一行動のため、結果として付いてくる。
+　到達水準は、主催に言っていただいた「月50万」を置く。
+　自分から追いはしないが、この道の先にその水準があることを前提に実践する。</t>
         </is>
       </c>
       <c r="D14" s="127" t="n"/>

--- a/_ JV攻略マイルストーン ワークシート.xlsx
+++ b/_ JV攻略マイルストーン ワークシート.xlsx
@@ -4703,9 +4703,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B2:D2"/>
     <mergeCell ref="B8:B13"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B5:B7"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5319,8 +5319,9 @@
       </c>
       <c r="F5" s="258" t="inlineStr">
         <is>
-          <t>苦しい副業から抜け出したい人へ、noteを入り口にメルマガで教育・販売するコンテンツビジネスの仕組みづくりを提供しています。
-集客・教育・販売をAIで半自動化し、時間と労力をかけずに安定して売上を生む形を目指します。</t>
+          <t>プレダイのコミュニティで、note を入り口に「ゼロイチ（初めての売上）」を達成するための講座と支援を提供します。
+記事の作成から販売までを Claude Code と自作AIツールで半自動化し、
+実績ゼロ・フォロワー0の状態から、最小の労力で最初の1円を作れる形を目指します。</t>
         </is>
       </c>
     </row>
@@ -5344,7 +5345,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="24" customHeight="1" s="272">
+    <row r="7" ht="30" customHeight="1" s="272">
       <c r="A7" s="141" t="n"/>
       <c r="B7" s="287" t="n"/>
       <c r="C7" s="285" t="inlineStr">
@@ -5360,11 +5361,12 @@
       </c>
       <c r="F7" s="258" t="inlineStr">
         <is>
-          <t>看護師（10年以上・訪問看護）。AI関連の資格はなし（ツールは10個以上を自作）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1" s="272">
+          <t>看護師（10年以上・訪問看護）。
+AI関連の資格はなし。Claude Code を用いた自作ツールが10個以上。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1" s="272">
       <c r="A8" s="141" t="n"/>
       <c r="B8" s="287" t="n"/>
       <c r="C8" s="285" t="inlineStr">
@@ -5381,11 +5383,12 @@
       <c r="F8" s="258" t="inlineStr">
         <is>
           <t>失敗は「家族への最高の贈り物」に変えられる。
-自己流の空回りを、正しい努力の方向性と仕組みに変えて自由を目指す。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1" s="272">
+自己流の空回りを、正しい努力の方向性と仕組みに変えて自由を目指す。
+最初の1円は、才能ではなく手順で作れる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="62" customHeight="1" s="272">
       <c r="A9" s="141" t="n"/>
       <c r="B9" s="287" t="n"/>
       <c r="C9" s="285" t="inlineStr">
@@ -5401,8 +5404,10 @@
       </c>
       <c r="F9" s="258" t="inlineStr">
         <is>
-          <t>過去の失敗で罪悪感を抱えながらも堅実に再起を目指す、note収益化の初心者。
-自己流で頑張っても稼げず、正しい方向性を探している人。</t>
+          <t>【JV先】プレダイ運営。
+【受講生】プレダイのメンバーのうち、まだ売上が0円のゼロイチ未達層。
+　過去の失敗で罪悪感を抱えながらも堅実に再起を目指し、
+　自己流で頑張っても稼げず、正しい方向性を探している人。</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5433,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1" s="272">
+    <row r="11" ht="76" customHeight="1" s="272">
       <c r="A11" s="141" t="n"/>
       <c r="B11" s="287" t="n"/>
       <c r="C11" s="285" t="inlineStr">
@@ -5447,10 +5452,10 @@
       </c>
       <c r="F11" s="258" t="inlineStr">
         <is>
-          <t>・note集客×メルマガ教育・販売の型（実践ベース）
-・ステップメール6教育、LP4段構成
-・自作AIツール（文章生成・LP作成・SNS自動投稿など）
-・自分の文体を学習させたAIライティング
+          <t>・note でゼロイチを達成するまでの手順（自分の実証をもとに体系化）
+・Claude Code ベースの自作AIツール（記事生成・LP作成・SNS自動投稿など10個以上）
+・Claude Code とツールの使い方レクチャー（受講生が自走できるまで）
+・ステップメール6教育／LP4段構成のノウハウ
 ・noteフォロワー約9,000人／メルマガ約300人への発信</t>
         </is>
       </c>
@@ -5477,9 +5482,10 @@
       </c>
       <c r="F12" s="258" t="inlineStr">
         <is>
-          <t>・裏方の設計・構築が得意。LP・ステップメール・特典・細かな設定・分析まで一気通貫で支援できます。
-・看護で鍛えた観察力と傾聴・寄り添う力で、相手や読者の状態を掴んで必要な支援を組み立てます。
-・全導線をAIで効率化。自分の文体を保ったまま、ライティングの型も効かせた文章を高速で用意できます。</t>
+          <t>・看護で鍛えた観察力と傾聴・寄り添う力で、受講生がどこで詰まっているかを言葉になる前に掴めます。
+・裏方の設計・構築が得意。手順書・テンプレート・ツールまで一気通貫で用意できます。
+・全工程をAIで効率化。自分の文体を保ったまま、型を効かせた文章を高速で用意できます。
+・自分自身がゼロイチで躓いた経験があるため、初心者がつまずく箇所を具体的に説明できます。</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5506,7 @@
       <c r="F13" s="260" t="inlineStr">
         <is>
           <t>対面での強いクロージング（押し売り）は苦手。
-当面は設計・構築を担当し、クロージングは相手やチームと分担したい（将来的に克服予定）。</t>
+教える・支える役割に集中したい（将来的に克服予定）。</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5557,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="36" customHeight="1" s="272">
+    <row r="16" ht="40" customHeight="1" s="272">
       <c r="A16" s="144" t="n"/>
       <c r="B16" s="287" t="n"/>
       <c r="C16" s="285" t="inlineStr">
@@ -5568,12 +5574,12 @@
       </c>
       <c r="F16" s="258" t="inlineStr">
         <is>
-          <t>年単位で組み続けられるWin-Winの関係。
-自分のステージを上げてくれて、購入者にきちんと寄り添える相手と長期で組みたい。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="60" customHeight="1" s="272">
+          <t>プレダイの note 講師として、年単位で運営に貢献し続けられる関係を築くこと。
+単発の講座提供ではなく、ゼロイチ層がコミュニティ内で次の段階へ進める導線をつくる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="76" customHeight="1" s="272">
       <c r="A17" s="144" t="n"/>
       <c r="B17" s="287" t="n"/>
       <c r="C17" s="285" t="inlineStr">
@@ -5593,8 +5599,10 @@
       </c>
       <c r="F17" s="258" t="inlineStr">
         <is>
-          <t>教育〜販売の設計・構築（LP・ステップメール・特典・導線）とAI自動化を担当。
-相手の集客力に、売れる仕組みを掛け合わせて成果を最大化する。</t>
+          <t>① 受講生をゼロイチに到達させること（低労力・低負荷での再現性まで含めて）
+② note講座を運営に渡せる形で確立すること（手順書・ツール・レクチャー一式）
+③ 実証データ（達成率・所要日数・総作業時間）を記録し、運営に提示すること
+※ 当面は自分の売上を追わず、運営へのギブを最優先にする。</t>
         </is>
       </c>
     </row>
@@ -5620,8 +5628,9 @@
       <c r="F18" s="258" t="inlineStr">
         <is>
           <t>・note フォロワー約9,000人／メルマガ約300人
+・サブアカウント（フォロワー900人強）で有料noteを販売し、5日で初売上を達成
 ・看護師歴10年以上（訪問看護・幅広い診療科）
-・自作AIツール10個以上
+・Claude Code を用いた自作AIツール10個以上
 ・Kindle出版（進行中）</t>
         </is>
       </c>
@@ -5650,7 +5659,7 @@
         <is>
           <t>・文章だけで「人柄を信じて購入します」と言われる
 ・「無料でここまで体系化された情報は初めて」と言われる
-※具体的な販売実績は要記入（本人）</t>
+※ 具体的な販売実績（金額・件数）は要記入（本人）</t>
         </is>
       </c>
     </row>
@@ -5670,7 +5679,7 @@
       </c>
       <c r="F20" s="258" t="inlineStr">
         <is>
-          <t>※要記入（本人）／短期目標は月9万円</t>
+          <t>※要記入（本人）</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5723,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="24" customHeight="1" s="272">
+    <row r="23" ht="30" customHeight="1" s="272">
       <c r="A23" s="144" t="n"/>
       <c r="B23" s="287" t="n"/>
       <c r="C23" s="285" t="inlineStr">
@@ -5738,7 +5747,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="272">
+    <row r="24" ht="30" customHeight="1" s="272">
       <c r="A24" s="144" t="n"/>
       <c r="B24" s="287" t="n"/>
       <c r="C24" s="277" t="n"/>
@@ -5754,11 +5763,12 @@
       </c>
       <c r="F24" s="258" t="inlineStr">
         <is>
-          <t>段階的に値上げ（モニター3,000円→定価49,800円）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="272">
+          <t>段階的に値上げ（モニター3,000円→定価49,800円）
+※ 実証用に、特典なし・100円版を新規アカウントで販売予定</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1" s="272">
       <c r="A25" s="144" t="n"/>
       <c r="B25" s="287" t="n"/>
       <c r="C25" s="285" t="inlineStr">
@@ -5778,7 +5788,7 @@
       </c>
       <c r="F25" s="258" t="inlineStr">
         <is>
-          <t>バックエンド商品（メルマガ販売の講座・コンサル）※作成中</t>
+          <t>note ゼロイチ講座＋伴走（Claude Code・自作AIツール・レクチャー込み）※開発中</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5808,7 @@
       </c>
       <c r="F26" s="258" t="inlineStr">
         <is>
-          <t>45,000円（短期の主力）／中期は240,000円</t>
+          <t>モニター価格は検討中／バックエンドは45,000円（中期240,000円）</t>
         </is>
       </c>
     </row>
@@ -5865,11 +5875,11 @@
       </c>
       <c r="F29" s="258" t="inlineStr">
         <is>
-          <t>note／メルマガ／公式LINE／Kindle／スタエフ／X・SNS</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="272">
+          <t>note／メルマガ／公式LINE／Kindle／スタエフ／X・SNS／プレダイのコミュニティ</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1" s="272">
       <c r="A30" s="144" t="n"/>
       <c r="B30" s="287" t="n"/>
       <c r="C30" s="285" t="inlineStr">
@@ -5885,7 +5895,7 @@
       </c>
       <c r="F30" s="258" t="inlineStr">
         <is>
-          <t>noteフォロワー約9,000人（＋X・SNS）</t>
+          <t>noteフォロワー約9,000人（メイン）＋サブアカウント900人強（＋X・SNS）</t>
         </is>
       </c>
     </row>
@@ -5931,7 +5941,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="24" customHeight="1" s="272">
+    <row r="33" ht="30" customHeight="1" s="272">
       <c r="A33" s="144" t="n"/>
       <c r="B33" s="287" t="n"/>
       <c r="C33" s="285" t="inlineStr">
@@ -5948,7 +5958,8 @@
       </c>
       <c r="F33" s="258" t="inlineStr">
         <is>
-          <t>※要記入（本人）</t>
+          <t>※要記入（本人）
+※ 実証モニター実施後に、受講生数・達成者数を記入する</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5983,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="36" customHeight="1" s="272">
+    <row r="35" ht="48" customHeight="1" s="272">
       <c r="A35" s="144" t="n"/>
       <c r="B35" s="287" t="n"/>
       <c r="C35" s="285" t="inlineStr">
@@ -5990,7 +6001,7 @@
       <c r="F35" s="258" t="inlineStr">
         <is>
           <t>価値観が合い、長期でWin-Winに組める人。
-集客力はあるが教育〜販売の仕組み化に課題がある発信者。
+ゼロイチで止まっているメンバーを本気で先に進めたいと考えている運営・講師。
 自分のステージを上げてくれる人。</t>
         </is>
       </c>

--- a/_ JV攻略マイルストーン ワークシート.xlsx
+++ b/_ JV攻略マイルストーン ワークシート.xlsx
@@ -4703,10 +4703,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C4:D4"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B8:B13"/>
-    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B5:B7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5320,7 +5320,7 @@
       <c r="F5" s="258" t="inlineStr">
         <is>
           <t>プレダイのコミュニティで、note を入り口に「ゼロイチ（初めての売上）」を達成するための講座と支援を提供します。
-記事の作成から販売までを Claude Code と自作AIツールで半自動化し、
+有料note販売のノウハウと note の仕組み構築方法に、集客に必要な毎日投稿を自動化するAIツールを掛け合わせ、
 実績ゼロ・フォロワー0の状態から、最小の労力で最初の1円を作れる形を目指します。</t>
         </is>
       </c>
@@ -5433,7 +5433,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="76" customHeight="1" s="272">
+    <row r="11" ht="150" customHeight="1" s="272">
       <c r="A11" s="141" t="n"/>
       <c r="B11" s="287" t="n"/>
       <c r="C11" s="285" t="inlineStr">
@@ -5452,11 +5452,16 @@
       </c>
       <c r="F11" s="258" t="inlineStr">
         <is>
-          <t>・note でゼロイチを達成するまでの手順（自分の実証をもとに体系化）
-・Claude Code ベースの自作AIツール（記事生成・LP作成・SNS自動投稿など10個以上）
+          <t>【noteの仕組み】
+・有料note販売のノウハウ（自分の実証をもとに体系化）
+・noteの仕組み構築方法（記事 → 導線 → 販売までの組み立て方）
+【AIの仕組み】
+・集客に必要な毎日投稿を自動化するAIツール（Claude Code ベース／10個以上を自作）
+・自分の文体を学習させたAIライティング
+【提供の形】
 ・Claude Code とツールの使い方レクチャー（受講生が自走できるまで）
-・ステップメール6教育／LP4段構成のノウハウ
-・noteフォロワー約9,000人／メルマガ約300人への発信</t>
+・noteフォロワー約9,000人／メルマガ約300人への発信
+※ 「noteの仕組み × AIの仕組み」を掛け合わせるのが提供価値の核。</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5664,7 @@
         <is>
           <t>・文章だけで「人柄を信じて購入します」と言われる
 ・「無料でここまで体系化された情報は初めて」と言われる
-※ 具体的な販売実績（金額・件数）は要記入（本人）</t>
+※ 講座としての顧客実績はこれから。コミュニティ内のモニターで成果を作り、ここに記入する。</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5684,7 @@
       </c>
       <c r="F20" s="258" t="inlineStr">
         <is>
-          <t>※要記入（本人）</t>
+          <t>5,000〜10,000円</t>
         </is>
       </c>
     </row>
@@ -5699,7 +5704,7 @@
       </c>
       <c r="F21" s="258" t="inlineStr">
         <is>
-          <t>※要記入（本人）</t>
+          <t>約6〜12万円（平均月商から算出）</t>
         </is>
       </c>
     </row>
@@ -5719,7 +5724,7 @@
       </c>
       <c r="F22" s="258" t="inlineStr">
         <is>
-          <t>※要記入（本人）</t>
+          <t>有料noteの販売のみ</t>
         </is>
       </c>
     </row>

--- a/_ JV攻略マイルストーン ワークシート.xlsx
+++ b/_ JV攻略マイルストーン ワークシート.xlsx
@@ -4703,10 +4703,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B5:B7"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B8:B13"/>
-    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C4:D4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5433,7 +5433,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="150" customHeight="1" s="272">
+    <row r="11" ht="190" customHeight="1" s="272">
       <c r="A11" s="141" t="n"/>
       <c r="B11" s="287" t="n"/>
       <c r="C11" s="285" t="inlineStr">
@@ -5455,9 +5455,12 @@
           <t>【noteの仕組み】
 ・有料note販売のノウハウ（自分の実証をもとに体系化）
 ・noteの仕組み構築方法（記事 → 導線 → 販売までの組み立て方）
-【AIの仕組み】
-・集客に必要な毎日投稿を自動化するAIツール（Claude Code ベース／10個以上を自作）
-・自分の文体を学習させたAIライティング
+【AIの仕組み｜note特化のツール一式（Claude Code ベース）】
+・売れている有料記事のリサーチ／投稿の構成作り
+・アカウント名／プロフィール／自己紹介文の作成
+・有料記事のセールス部分＋有料部分の作成／特典の作成
+・毎日投稿の自動化（集客）／自分の文体を学習させたAIライティング
+・ヘッダー画像（※本人による代行制作を検討中）
 【提供の形】
 ・Claude Code とツールの使い方レクチャー（受講生が自走できるまで）
 ・noteフォロワー約9,000人／メルマガ約300人への発信
@@ -6126,7 +6129,7 @@
       <c r="A5" s="139" t="n"/>
       <c r="B5" s="149" t="n"/>
     </row>
-    <row r="6" ht="28.5" customHeight="1" s="272">
+    <row r="6" ht="34" customHeight="1" s="272">
       <c r="A6" s="139" t="n"/>
       <c r="B6" s="150" t="inlineStr">
         <is>
@@ -6135,8 +6138,8 @@
       </c>
       <c r="C6" s="294" t="inlineStr">
         <is>
-          <t>過去の失敗を「価値」に変えて罪悪感から解放され、
-自分の力で家族に経済的な安心と笑顔を届けられるようになる。</t>
+          <t>実績もフォロワーもゼロの状態から、最初の1円を自分の手で作れるようになる。
+そしてその過程で、過去の失敗が「売れる価値」に変わり、罪悪感から解放される。</t>
         </is>
       </c>
       <c r="D6" s="274" t="n"/>
@@ -6503,110 +6506,284 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="45" customHeight="1" s="272">
       <c r="A28" s="159" t="n"/>
-      <c r="B28" s="299" t="n"/>
-      <c r="C28" s="304" t="n"/>
-      <c r="D28" s="160" t="n"/>
-      <c r="E28" s="160" t="n"/>
-    </row>
-    <row r="29">
+      <c r="B28" s="297" t="inlineStr">
+        <is>
+          <t>note の有料販売ノウハウ
+（フォロワー900人強のサブアカで実証・5日で初売上）</t>
+        </is>
+      </c>
+      <c r="C28" s="313" t="inlineStr">
+        <is>
+          <t>「まだ誰にも知られていない自分」でも、
+最初の1円が立つ手順が分かる</t>
+        </is>
+      </c>
+      <c r="D28" s="265" t="inlineStr">
+        <is>
+          <t>まだ1円も稼げていない人</t>
+        </is>
+      </c>
+      <c r="E28" s="265" t="inlineStr">
+        <is>
+          <t>「自分にも売れた」という事実が手に入り、次に進む足場ができる</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="34" customHeight="1" s="272">
       <c r="A29" s="159" t="n"/>
       <c r="B29" s="287" t="n"/>
       <c r="C29" s="287" t="n"/>
-      <c r="D29" s="161" t="n"/>
-      <c r="E29" s="161" t="n"/>
-    </row>
-    <row r="30">
+      <c r="D29" s="265" t="inlineStr">
+        <is>
+          <t>何を売ればいいか分からない人</t>
+        </is>
+      </c>
+      <c r="E29" s="265" t="inlineStr">
+        <is>
+          <t>題材の決め方から手順になっているので、ゼロから作れる</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="34" customHeight="1" s="272">
       <c r="A30" s="159" t="n"/>
       <c r="B30" s="277" t="n"/>
       <c r="C30" s="277" t="n"/>
-      <c r="D30" s="162" t="n"/>
-      <c r="E30" s="162" t="n"/>
-    </row>
-    <row r="31">
+      <c r="D30" s="265" t="inlineStr">
+        <is>
+          <t>高額商品を作る自信がない人</t>
+        </is>
+      </c>
+      <c r="E30" s="265" t="inlineStr">
+        <is>
+          <t>少額から始められるので、心理的なハードルなく踏み出せる</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="45" customHeight="1" s="272">
       <c r="A31" s="159" t="n"/>
-      <c r="B31" s="300" t="n"/>
-      <c r="C31" s="295" t="n"/>
-      <c r="D31" s="160" t="n"/>
-      <c r="E31" s="160" t="n"/>
-    </row>
-    <row r="32">
+      <c r="B31" s="297" t="inlineStr">
+        <is>
+          <t>note の仕組み構築方法
+（記事 → 導線 → 販売の組み立て）</t>
+        </is>
+      </c>
+      <c r="C31" s="313" t="inlineStr">
+        <is>
+          <t>単発の記事投稿ではなく、
+読まれてから買われるまでが一本につながる</t>
+        </is>
+      </c>
+      <c r="D31" s="265" t="inlineStr">
+        <is>
+          <t>記事は書けるのに売上にならない人</t>
+        </is>
+      </c>
+      <c r="E31" s="265" t="inlineStr">
+        <is>
+          <t>書いた記事が販売につながる形に変わる</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="34" customHeight="1" s="272">
       <c r="A32" s="159" t="n"/>
       <c r="B32" s="287" t="n"/>
       <c r="C32" s="287" t="n"/>
-      <c r="D32" s="163" t="n"/>
-      <c r="E32" s="163" t="n"/>
-    </row>
-    <row r="33">
+      <c r="D32" s="265" t="inlineStr">
+        <is>
+          <t>フォロワーが増えても収益化できない人</t>
+        </is>
+      </c>
+      <c r="E32" s="265" t="inlineStr">
+        <is>
+          <t>数を追わなくても、少ない読者から売上が立つ</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="34" customHeight="1" s="272">
       <c r="A33" s="159" t="n"/>
       <c r="B33" s="277" t="n"/>
       <c r="C33" s="277" t="n"/>
-      <c r="D33" s="162" t="n"/>
-      <c r="E33" s="162" t="n"/>
-    </row>
-    <row r="34">
+      <c r="D33" s="265" t="inlineStr">
+        <is>
+          <t>何から手をつけるか分からない人</t>
+        </is>
+      </c>
+      <c r="E33" s="265" t="inlineStr">
+        <is>
+          <t>組み立ての順番が決まっているので迷わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="96" customHeight="1" s="272">
       <c r="A34" s="159" t="n"/>
-      <c r="B34" s="300" t="n"/>
-      <c r="C34" s="295" t="n"/>
-      <c r="D34" s="160" t="n"/>
-      <c r="E34" s="160" t="n"/>
-    </row>
-    <row r="35">
+      <c r="B34" s="297" t="inlineStr">
+        <is>
+          <t>note に特化したAIツール一式（Claude Code ベース）
+・売れている有料記事のリサーチ　・投稿の構成作り
+・アカウント名／プロフィール／自己紹介文の作成
+・有料記事のセールス部分＋有料部分の作成　・特典の作成
+・ヘッダー画像（※本人による代行制作を検討中）</t>
+        </is>
+      </c>
+      <c r="C34" s="313" t="inlineStr">
+        <is>
+          <t>note でゼロイチに必要な作業が、
+リサーチからアカウント設計、記事・特典の作成まで
+一式そろっている</t>
+        </is>
+      </c>
+      <c r="D34" s="265" t="inlineStr">
+        <is>
+          <t>何が売れるのか分からない人</t>
+        </is>
+      </c>
+      <c r="E34" s="265" t="inlineStr">
+        <is>
+          <t>売れている有料記事のリサーチから始められるので、当てずっぽうで書かずに済む</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1" s="272">
       <c r="A35" s="159" t="n"/>
       <c r="B35" s="287" t="n"/>
       <c r="C35" s="287" t="n"/>
-      <c r="D35" s="163" t="n"/>
-      <c r="E35" s="163" t="n"/>
-    </row>
-    <row r="36">
+      <c r="D35" s="265" t="inlineStr">
+        <is>
+          <t>アカウントの見た目に自信がない人</t>
+        </is>
+      </c>
+      <c r="E35" s="265" t="inlineStr">
+        <is>
+          <t>アカウント名・プロフィール・自己紹介文・ヘッダーまで整い、初日から「買ってもいい人」に見える</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="34" customHeight="1" s="272">
       <c r="A36" s="159" t="n"/>
       <c r="B36" s="277" t="n"/>
       <c r="C36" s="277" t="n"/>
-      <c r="D36" s="162" t="n"/>
-      <c r="E36" s="162" t="n"/>
-    </row>
-    <row r="37">
+      <c r="D36" s="265" t="inlineStr">
+        <is>
+          <t>有料部分をどう書けばいいか分からない人</t>
+        </is>
+      </c>
+      <c r="E36" s="265" t="inlineStr">
+        <is>
+          <t>セールス部分と有料部分の作成まで道具があるので、書き方で止まらない</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="45" customHeight="1" s="272">
       <c r="A37" s="159" t="n"/>
-      <c r="B37" s="300" t="n"/>
-      <c r="C37" s="295" t="n"/>
-      <c r="D37" s="160" t="n"/>
-      <c r="E37" s="160" t="n"/>
-    </row>
-    <row r="38">
+      <c r="B37" s="297" t="inlineStr">
+        <is>
+          <t>Claude Code とツールの使い方レクチャー
+（自走できるまで伴走）</t>
+        </is>
+      </c>
+      <c r="C37" s="313" t="inlineStr">
+        <is>
+          <t>ツールを渡すだけで終わらせず、
+受講生が自分で回せる状態まで持っていく</t>
+        </is>
+      </c>
+      <c r="D37" s="265" t="inlineStr">
+        <is>
+          <t>AIツールが難しそうで手が出ない人</t>
+        </is>
+      </c>
+      <c r="E37" s="265" t="inlineStr">
+        <is>
+          <t>導入から操作まで教わるので、初日から使える</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="34" customHeight="1" s="272">
       <c r="A38" s="159" t="n"/>
       <c r="B38" s="287" t="n"/>
       <c r="C38" s="287" t="n"/>
-      <c r="D38" s="163" t="n"/>
-      <c r="E38" s="163" t="n"/>
-    </row>
-    <row r="39">
+      <c r="D38" s="265" t="inlineStr">
+        <is>
+          <t>過去に教材を買って放置した人</t>
+        </is>
+      </c>
+      <c r="E38" s="265" t="inlineStr">
+        <is>
+          <t>使えるようになるまで伴走するので、積読にならない</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="34" customHeight="1" s="272">
       <c r="A39" s="159" t="n"/>
       <c r="B39" s="277" t="n"/>
       <c r="C39" s="277" t="n"/>
-      <c r="D39" s="162" t="n"/>
-      <c r="E39" s="162" t="n"/>
-    </row>
-    <row r="40">
+      <c r="D39" s="265" t="inlineStr">
+        <is>
+          <t>一人だと詰まって止まる人</t>
+        </is>
+      </c>
+      <c r="E39" s="265" t="inlineStr">
+        <is>
+          <t>詰まる箇所が分かっているので、すぐ解消できる</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="45" customHeight="1" s="272">
       <c r="A40" s="159" t="n"/>
-      <c r="B40" s="300" t="n"/>
-      <c r="C40" s="295" t="n"/>
-      <c r="D40" s="160" t="n"/>
-      <c r="E40" s="160" t="n"/>
-    </row>
-    <row r="41">
+      <c r="B40" s="297" t="inlineStr">
+        <is>
+          <t>講師自身も新規0フォロワーアカウントで
+同じ手順を実行・検証していること</t>
+        </is>
+      </c>
+      <c r="C40" s="313" t="inlineStr">
+        <is>
+          <t>「教える人」ではなく
+「同じ条件で走っている人」として手順を渡せる</t>
+        </is>
+      </c>
+      <c r="D40" s="265" t="inlineStr">
+        <is>
+          <t>成功者の話が現実離れして感じる人</t>
+        </is>
+      </c>
+      <c r="E40" s="265" t="inlineStr">
+        <is>
+          <t>今まさに同じ地点を通っている人の手順が手に入る</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="34" customHeight="1" s="272">
       <c r="A41" s="159" t="n"/>
       <c r="B41" s="287" t="n"/>
       <c r="C41" s="287" t="n"/>
-      <c r="D41" s="163" t="n"/>
-      <c r="E41" s="163" t="n"/>
-    </row>
-    <row r="42">
+      <c r="D41" s="265" t="inlineStr">
+        <is>
+          <t>古い情報を掴まされた経験がある人</t>
+        </is>
+      </c>
+      <c r="E41" s="265" t="inlineStr">
+        <is>
+          <t>現在進行形で検証された手順なので、鮮度が担保される</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="34" customHeight="1" s="272">
       <c r="A42" s="159" t="n"/>
       <c r="B42" s="277" t="n"/>
       <c r="C42" s="277" t="n"/>
-      <c r="D42" s="162" t="n"/>
-      <c r="E42" s="162" t="n"/>
+      <c r="D42" s="265" t="inlineStr">
+        <is>
+          <t>質問しても曖昧な答えしか返ってこなかった人</t>
+        </is>
+      </c>
+      <c r="E42" s="265" t="inlineStr">
+        <is>
+          <t>詰まる箇所を実体験として把握しているので、具体的に答えてもらえる</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="3.75" customHeight="1" s="272"/>
   </sheetData>

--- a/_ JV攻略マイルストーン ワークシート.xlsx
+++ b/_ JV攻略マイルストーン ワークシート.xlsx
@@ -4703,10 +4703,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C4:D4"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B8:B13"/>
-    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B5:B7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7127,9 +7127,13 @@
       <c r="D22" s="181" t="n"/>
       <c r="E22" s="318" t="n"/>
     </row>
-    <row r="23" ht="12.75" customHeight="1" s="272">
+    <row r="23" ht="13" customHeight="1" s="272">
       <c r="B23" s="277" t="n"/>
-      <c r="C23" s="182" t="n"/>
+      <c r="C23" s="182" t="inlineStr">
+        <is>
+          <t>＜ ゼロイチで止まり、最初の1円が作れないという課題 ＞</t>
+        </is>
+      </c>
       <c r="D23" s="183" t="inlineStr">
         <is>
           <t>を満たしたい／解決したい</t>
@@ -7137,13 +7141,17 @@
       </c>
       <c r="E23" s="318" t="n"/>
     </row>
-    <row r="24" ht="12.75" customHeight="1" s="272">
+    <row r="24" ht="13" customHeight="1" s="272">
       <c r="B24" s="285" t="inlineStr">
         <is>
           <t xml:space="preserve"> ❷ 対象客</t>
         </is>
       </c>
-      <c r="C24" s="184" t="n"/>
+      <c r="C24" s="184" t="inlineStr">
+        <is>
+          <t>＜ プレダイのメンバーのうち、まだ売上が0円のゼロイチ未達層 ＞</t>
+        </is>
+      </c>
       <c r="D24" s="185" t="inlineStr">
         <is>
           <t>向けの、</t>
@@ -7151,13 +7159,17 @@
       </c>
       <c r="E24" s="318" t="n"/>
     </row>
-    <row r="25" ht="12.75" customHeight="1" s="272">
+    <row r="25" ht="13" customHeight="1" s="272">
       <c r="B25" s="285" t="inlineStr">
         <is>
           <t xml:space="preserve"> ❸ 商品・サービス名</t>
         </is>
       </c>
-      <c r="C25" s="184" t="n"/>
+      <c r="C25" s="184" t="inlineStr">
+        <is>
+          <t>＜ note ゼロイチ講座（note特化のAIツール一式＋レクチャー付き） ＞</t>
+        </is>
+      </c>
       <c r="D25" s="185" t="inlineStr">
         <is>
           <t>という、</t>
@@ -7165,13 +7177,17 @@
       </c>
       <c r="E25" s="318" t="n"/>
     </row>
-    <row r="26" ht="12.75" customHeight="1" s="272">
+    <row r="26" ht="13" customHeight="1" s="272">
       <c r="B26" s="285" t="inlineStr">
         <is>
           <t xml:space="preserve"> ❹ 商品・サービスのカテゴリ</t>
         </is>
       </c>
-      <c r="C26" s="184" t="n"/>
+      <c r="C26" s="184" t="inlineStr">
+        <is>
+          <t>＜ note × AI によるゼロイチ支援 ＞</t>
+        </is>
+      </c>
       <c r="D26" s="185" t="inlineStr">
         <is>
           <t>である。</t>
@@ -7193,9 +7209,13 @@
       <c r="D27" s="187" t="n"/>
       <c r="E27" s="318" t="n"/>
     </row>
-    <row r="28" ht="12.75" customHeight="1" s="272">
+    <row r="28" ht="13" customHeight="1" s="272">
       <c r="B28" s="277" t="n"/>
-      <c r="C28" s="182" t="n"/>
+      <c r="C28" s="182" t="inlineStr">
+        <is>
+          <t>＜ 実績もフォロワーもゼロの状態から、最初の1円を自分の手で作ること ＞</t>
+        </is>
+      </c>
       <c r="D28" s="183" t="inlineStr">
         <is>
           <t>ができる。</t>
@@ -7203,13 +7223,17 @@
       </c>
       <c r="E28" s="318" t="n"/>
     </row>
-    <row r="29" ht="12.75" customHeight="1" s="272">
+    <row r="29" ht="13" customHeight="1" s="272">
       <c r="B29" s="285" t="inlineStr">
         <is>
           <t xml:space="preserve"> ❻ 大半のユーザーの頭にある商品・サービス</t>
         </is>
       </c>
-      <c r="C29" s="184" t="n"/>
+      <c r="C29" s="184" t="inlineStr">
+        <is>
+          <t>＜ 自己流のnote運用や、媒体を限定しない一般的なゼロイチ講座 ＞</t>
+        </is>
+      </c>
       <c r="D29" s="185" t="inlineStr">
         <is>
           <t>とは違って、</t>
@@ -7217,13 +7241,18 @@
       </c>
       <c r="E29" s="318" t="n"/>
     </row>
-    <row r="30" ht="12.75" customHeight="1" s="272">
+    <row r="30" ht="28" customHeight="1" s="272">
       <c r="B30" s="288" t="inlineStr">
         <is>
           <t xml:space="preserve"> ❼ 差別化の決定的な特徴</t>
         </is>
       </c>
-      <c r="C30" s="188" t="n"/>
+      <c r="C30" s="188" t="inlineStr">
+        <is>
+          <t>＜ note に特化したAIツール一式で、リサーチからアカウント設計、
+　 記事・特典の作成までを肩代わりし、少ない作業時間で最初の1円に到達できること ＞</t>
+        </is>
+      </c>
       <c r="D30" s="189" t="inlineStr">
         <is>
           <t>が備わっている。</t>
@@ -7245,9 +7274,13 @@
       <c r="D31" s="190" t="n"/>
       <c r="E31" s="318" t="n"/>
     </row>
-    <row r="32" ht="12.75" customHeight="1" s="272">
+    <row r="32" ht="13" customHeight="1" s="272">
       <c r="B32" s="277" t="n"/>
-      <c r="C32" s="182" t="n"/>
+      <c r="C32" s="182" t="inlineStr">
+        <is>
+          <t>＜ note という具体的な媒体に特化した講座 ＞</t>
+        </is>
+      </c>
       <c r="D32" s="183" t="inlineStr">
         <is>
           <t>を補完できます。</t>
@@ -7269,9 +7302,14 @@
       <c r="D33" s="187" t="n"/>
       <c r="E33" s="318" t="n"/>
     </row>
-    <row r="34" ht="12.75" customHeight="1" s="272">
+    <row r="34" ht="28" customHeight="1" s="272">
       <c r="B34" s="277" t="n"/>
-      <c r="C34" s="182" t="n"/>
+      <c r="C34" s="182" t="inlineStr">
+        <is>
+          <t>＜ ゼロイチで止まっていたメンバーが次の段階へ進み、
+　 コミュニティの本編（JV・サミット等）に乗れるようになります ＞</t>
+        </is>
+      </c>
       <c r="D34" s="183" t="inlineStr">
         <is>
           <t>になります。</t>

--- a/_ JV攻略マイルストーン ワークシート.xlsx
+++ b/_ JV攻略マイルストーン ワークシート.xlsx
@@ -29,7 +29,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m\-d"/>
   </numFmts>
-  <fonts count="76">
+  <fonts count="77">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -477,6 +477,11 @@
       <color theme="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000000FF"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="37">
     <fill>
@@ -1476,7 +1481,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="362">
+  <cellXfs count="364">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2470,6 +2475,12 @@
     </xf>
     <xf numFmtId="164" fontId="36" fillId="19" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="6" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4703,10 +4714,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B5:B7"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B8:B13"/>
-    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C4:D4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9205,10 +9216,18 @@
       </c>
     </row>
     <row r="17" ht="12.75" customHeight="1" s="272">
-      <c r="B17" s="285" t="n"/>
+      <c r="B17" s="261" t="inlineStr">
+        <is>
+          <t>いきなり連絡してくる人（前触れも接点もなく本題から入る人）</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="12.75" customHeight="1" s="272">
-      <c r="B18" s="285" t="n"/>
+      <c r="B18" s="261" t="inlineStr">
+        <is>
+          <t>何を目的に連絡したのかを自ら明かさない人</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="12.75" customHeight="1" s="272">
       <c r="B19" s="285" t="n"/>
@@ -9284,9 +9303,13 @@
       <c r="R2" s="127" t="n"/>
       <c r="S2" s="127" t="n"/>
     </row>
-    <row r="3" ht="3.75" customHeight="1" s="272">
+    <row r="3" ht="26" customHeight="1" s="272">
       <c r="A3" s="127" t="n"/>
-      <c r="B3" s="1" t="n"/>
+      <c r="B3" s="362" t="inlineStr">
+        <is>
+          <t>※ JV先はプレダイ運営に確定したため、本シートは「受講生候補（プレダイのゼロイチ未達メンバー）のリサーチ」として使用する。　下段の購入前〜購入後は「モニター申込前〜受講中〜達成後」と読み替える。</t>
+        </is>
+      </c>
       <c r="C3" s="1" t="n"/>
       <c r="D3" s="127" t="n"/>
       <c r="E3" s="127" t="n"/>
@@ -9403,12 +9426,12 @@
 LINE配信</t>
         </is>
       </c>
-      <c r="D6" s="262" t="inlineStr">
-        <is>
-          <t>※現時点では未把握。
-読者から具体名が挙がったことはない。
-カテゴリとしては noteビジネス系／副業系／コンテンツビジネス系 の発信者と推定。
-→ 次アクション：メルマガ・noteで読者アンケートを取り、具体名を収集する</t>
+      <c r="D6" s="363" t="inlineStr">
+        <is>
+          <t>【読み替え】受講生候補が読んでいるもの
+仮説：プレダイ本体の配信が中心。加えて note ビジネス系・副業系の発信者。
+→ 次アクション：同じコミュニティに所属しているため直接観察できる。
+　 雑談・投稿から具体名を拾う。</t>
         </is>
       </c>
       <c r="E6" s="239" t="n"/>
@@ -9495,9 +9518,11 @@
 インフルエンサー</t>
         </is>
       </c>
-      <c r="D11" s="262" t="inlineStr">
-        <is>
-          <t>※未把握（上に同じ。読者アンケートで収集予定）</t>
+      <c r="D11" s="363" t="inlineStr">
+        <is>
+          <t>仮説：プレダイの主催・既存講師（特にゼロイチ講師）。
+外部インフルエンサーより、コミュニティ内の人物の影響力が強いと推定。
+→ 次アクション：誰の投稿に反応が集まっているかを観察する。</t>
         </is>
       </c>
       <c r="E11" s="239" t="n"/>
@@ -9576,7 +9601,7 @@
       <c r="N15" s="245" t="n"/>
       <c r="O15" s="127" t="n"/>
     </row>
-    <row r="16" ht="12.75" customHeight="1" s="272">
+    <row r="16" ht="20" customHeight="1" s="272">
       <c r="A16" s="127" t="n"/>
       <c r="C16" s="336" t="inlineStr">
         <is>
@@ -9584,7 +9609,14 @@
 (人・企業・本など)</t>
         </is>
       </c>
-      <c r="D16" s="337" t="n"/>
+      <c r="D16" s="363" t="inlineStr">
+        <is>
+          <t>仮説：コミュニティ内の成果報告と、同じ段階の仲間の体験談。
+外部の権威よりも「自分と近い人の実例」が効くと推定。
+→ 次アクション：成果報告投稿への反応を観察し、何が信頼されているかを特定する。
+　 モニター募集時に「同じ段階の人の実例」を見せる設計に使う。</t>
+        </is>
+      </c>
       <c r="E16" s="239" t="n"/>
       <c r="F16" s="239" t="n"/>
       <c r="G16" s="239" t="n"/>
@@ -9661,7 +9693,7 @@
       <c r="N20" s="245" t="n"/>
       <c r="O20" s="127" t="n"/>
     </row>
-    <row r="21" ht="12.75" customHeight="1" s="272">
+    <row r="21" ht="20" customHeight="1" s="272">
       <c r="A21" s="127" t="n"/>
       <c r="C21" s="336" t="inlineStr">
         <is>
@@ -9669,7 +9701,13 @@
 投稿・動画・記事</t>
         </is>
       </c>
-      <c r="D21" s="337" t="n"/>
+      <c r="D21" s="363" t="inlineStr">
+        <is>
+          <t>→ 次アクション：コミュニティ内でシェア・引用されている投稿を1週間分収集し、
+　 共通する型（数字／体験談／手順のどれが反応されるか）を特定する。
+　 モニター募集文の書き方の材料にする。</t>
+        </is>
+      </c>
       <c r="E21" s="239" t="n"/>
       <c r="F21" s="239" t="n"/>
       <c r="G21" s="239" t="n"/>
@@ -9746,7 +9784,7 @@
       <c r="N25" s="245" t="n"/>
       <c r="O25" s="127" t="n"/>
     </row>
-    <row r="26" ht="12.75" customHeight="1" s="272">
+    <row r="26" ht="20" customHeight="1" s="272">
       <c r="A26" s="127" t="n"/>
       <c r="C26" s="337" t="inlineStr">
         <is>
@@ -9754,7 +9792,13 @@
 競合商品やコミュニティ</t>
         </is>
       </c>
-      <c r="D26" s="337" t="n"/>
+      <c r="D26" s="363" t="inlineStr">
+        <is>
+          <t>仮説：プレダイ内の既存講座（特にゼロイチ系）、note・Brain 等の少額教材。
+→ 次アクション：価格帯と、購入者が何を期待して買ったかを把握する。
+　 モニター価格の設定根拠にする（現在「検討中」のまま）。</t>
+        </is>
+      </c>
       <c r="E26" s="239" t="n"/>
       <c r="F26" s="239" t="n"/>
       <c r="G26" s="239" t="n"/>
@@ -9962,14 +10006,21 @@
       </c>
       <c r="R33" s="127" t="n"/>
     </row>
-    <row r="34" ht="12.75" customHeight="1" s="272">
+    <row r="34" ht="20" customHeight="1" s="272">
       <c r="A34" s="127" t="n"/>
       <c r="C34" s="336" t="inlineStr">
         <is>
           <t>商品の購入前</t>
         </is>
       </c>
-      <c r="D34" s="337" t="n"/>
+      <c r="D34" s="363" t="inlineStr">
+        <is>
+          <t>【モニター申込前】
+仮説：「やってみたいが自分にできるか不安」「また買って終わりになるのが怖い」
+判断材料にするもの：講師自身の実績／同じ段階の人の成果／作業量の見通し
+→ 打ち手：段階0（自分の0フォロワー検証）の進捗を公開し、作業時間を数字で示す。</t>
+        </is>
+      </c>
       <c r="E34" s="239" t="n"/>
       <c r="F34" s="239" t="n"/>
       <c r="G34" s="239" t="n"/>
@@ -10061,14 +10112,22 @@
       <c r="Q38" s="245" t="n"/>
       <c r="R38" s="127" t="n"/>
     </row>
-    <row r="39" ht="12.75" customHeight="1" s="272">
+    <row r="39" ht="20" customHeight="1" s="272">
       <c r="A39" s="127" t="n"/>
       <c r="C39" s="336" t="inlineStr">
         <is>
           <t>商品の購入中</t>
         </is>
       </c>
-      <c r="D39" s="337" t="n"/>
+      <c r="D39" s="363" t="inlineStr">
+        <is>
+          <t>【受講中】
+仮説：離脱が起きるのは次の3点。
+　① ツールの操作でつまずく　② 題材が決まらない　③ 公開ボタンが押せない
+→ 打ち手：①は初回レクチャーで潰す。②は題材決定を独立した支援にする。
+　 実証ログの「つまずいたこと」欄で、実際の離脱点を特定する。</t>
+        </is>
+      </c>
       <c r="E39" s="239" t="n"/>
       <c r="F39" s="239" t="n"/>
       <c r="G39" s="239" t="n"/>
@@ -10160,14 +10219,21 @@
       <c r="Q43" s="245" t="n"/>
       <c r="R43" s="127" t="n"/>
     </row>
-    <row r="44" ht="12.75" customHeight="1" s="272">
+    <row r="44" ht="20" customHeight="1" s="272">
       <c r="A44" s="127" t="n"/>
       <c r="C44" s="337" t="inlineStr">
         <is>
           <t>商品の購入後</t>
         </is>
       </c>
-      <c r="D44" s="337" t="n"/>
+      <c r="D44" s="363" t="inlineStr">
+        <is>
+          <t>【達成後】
+仮説：「売れたが、次に何をすればいいか分からない」で止まる。
+→ 打ち手：ゼロイチ達成を終点にせず、コミュニティ本編（JV・サミット）への
+　 接続を最初から設計に含める。これが運営にとっての価値でもある。</t>
+        </is>
+      </c>
       <c r="E44" s="239" t="n"/>
       <c r="F44" s="239" t="n"/>
       <c r="G44" s="239" t="n"/>

--- a/_ JV攻略マイルストーン ワークシート.xlsx
+++ b/_ JV攻略マイルストーン ワークシート.xlsx
@@ -3540,7 +3540,7 @@
       </c>
       <c r="E4" s="127" t="n"/>
     </row>
-    <row r="5" ht="81.75" customHeight="1" s="272">
+    <row r="5" ht="90" customHeight="1" s="272">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="285" t="inlineStr">
         <is>
@@ -3556,14 +3556,16 @@
       </c>
       <c r="D5" s="258" t="inlineStr">
         <is>
-          <t>〇〇様の既存リストに向けたステップ配信（メルマガ／LINE）と、販売ページ（LP）の設計・構築を、
-私が裏方として無償でお手伝いさせていただけないでしょうか。
-まずはステップメール一式とLP構成案を、こちらで一度お作りします。</t>
+          <t>プレダイのメンバー向けに、note でゼロイチ（初めての売上）を達成するための講座を
+担当させていただけないでしょうか。
+すでに自費でモニター実証を行っており、第2陣◯名中◯名が◯日以内に初売上を達成しています。
+（平均総作業時間◯時間／全員が新規アカウント・フォロワー0からのスタート）
+※ ◯は実証完了後に記入する</t>
         </is>
       </c>
       <c r="E5" s="127" t="n"/>
     </row>
-    <row r="6" ht="81.75" customHeight="1" s="272">
+    <row r="6" ht="110" customHeight="1" s="272">
       <c r="A6" s="127" t="n"/>
       <c r="B6" s="285" t="inlineStr">
         <is>
@@ -3582,16 +3584,18 @@
       </c>
       <c r="D6" s="258" t="inlineStr">
         <is>
-          <t>〇〇様は高い集客力と発信の熱量をお持ちである一方、
-配信のたびに文章を一から書き起こすご負担や、
-集めた読者を売上につなげる導線が「仕組み」として固定化されていない点に
-課題をお持ちかと拝察しております。
-教育〜販売の型が入れば、今の集客力がそのまま成果に変わると考えております。</t>
+          <t>マイルストーン本編は「資産がある方」を前提に設計されており、
+ゼロイチ・スタート期の方は毎回EXルートへご案内される構造になっています。
+実績ゼロの層がここで足踏みしていることが、コミュニティ全体の進行における
+最大のボトルネックだと拝察しております。
+また、note に特化した講座は現在ラインナップにございません。
+既存のゼロイチ講座で方向性を掴まれた方が、note という具体的な媒体で
+最初の1円を作るところが空白になっていると考えております。</t>
         </is>
       </c>
       <c r="E6" s="127" t="n"/>
     </row>
-    <row r="7" ht="81.75" customHeight="1" s="272">
+    <row r="7" ht="118" customHeight="1" s="272">
       <c r="A7" s="127" t="n"/>
       <c r="B7" s="285" t="inlineStr">
         <is>
@@ -3607,15 +3611,19 @@
       </c>
       <c r="D7" s="258" t="inlineStr">
         <is>
-          <t>まずは無償で、ステップメール（6通程度）とLP構成案を2週間以内にご提出します。
-ご確認いただき、方向性が合うようでしたら、
-配信設定・特典作成・数値分析までを継続してお手伝いいたします。
-スケジュールは〇〇様のご都合に合わせて調整可能です。</t>
+          <t>【提供内容】
+・note ゼロイチの手順書（リサーチ → アカウント設計 → 有料記事作成 → 集客）
+・note 特化のAIツール一式（Claude Code ベース／11点）
+・Canva テンプレート集（固定記事・アカウントページのヘッダー用）
+・初回レクチャー（Claude Code とツールの使い方）※必須参加
+・期間中の質問対応
+【期間】受講生1名あたり1週間を想定（モニター実証の結果に基づく）
+【スケジュール】〇〇様のご都合に合わせて調整可能です。</t>
         </is>
       </c>
       <c r="E7" s="127" t="n"/>
     </row>
-    <row r="8" ht="81.75" customHeight="1" s="272">
+    <row r="8" ht="110" customHeight="1" s="272">
       <c r="A8" s="127" t="n"/>
       <c r="B8" s="285" t="inlineStr">
         <is>
@@ -3635,15 +3643,18 @@
       </c>
       <c r="D8" s="258" t="inlineStr">
         <is>
-          <t>〇〇様にとっては、追加コストゼロで教育〜販売の仕組みが手に入り、
-既存リストからの売上を伸ばせます。
-読者にとっては、必要な情報が順序立てて届き、納得したうえで商品を選べる状態になります。
-私にとっては実績と学びが得られます。三方よしの形だと考えております。</t>
+          <t>【運営様】ゼロイチで止まっていたメンバーが次の段階へ進み、
+　　　　　JV・サミットなど本編に乗れるようになります。
+　　　　　成果事例が増えることで、コミュニティの実績としても提示できます。
+【メンバー】実績もフォロワーもゼロの状態から、最初の1円を自分の手で作れます。
+　　　　　　少ない作業時間で到達できるため、本業を持ったままでも進められます。
+【私】講師としての実績と学びが得られます。
+三方よしの形だと考えております。</t>
         </is>
       </c>
       <c r="E8" s="127" t="n"/>
     </row>
-    <row r="9" ht="81.75" customHeight="1" s="272">
+    <row r="9" ht="100" customHeight="1" s="272">
       <c r="A9" s="127" t="n"/>
       <c r="B9" s="285" t="inlineStr">
         <is>
@@ -3660,16 +3671,17 @@
       </c>
       <c r="D9" s="258" t="inlineStr">
         <is>
-          <t>初回のステップメール・LP構成案は無償です。
+          <t>報酬の取り決めは、〇〇様のご判断に従います。
 正直にお伝えすると、私はいま実績を積み上げている段階です。
-成果を実感いただけたら「お客様の声」を一言いただけるだけで十分で、
-その上で継続やご紹介をご相談できれば嬉しいです。
-なお、リストは〇〇様に帰属し、私が持ち出すことは一切ございません。</t>
+当面は自分の売上を追うつもりはなく、運営にお返しすることを最優先に考えております。
+受講生・受講料の扱い、講座の権利関係についても、コミュニティの方針に合わせます。
+実証で得たデータ（達成率・所要日数・総作業時間・つまずいた箇所）は
+すべて開示いたします。</t>
         </is>
       </c>
       <c r="E9" s="127" t="n"/>
     </row>
-    <row r="10" ht="81.75" customHeight="1" s="272">
+    <row r="10" ht="90" customHeight="1" s="272">
       <c r="A10" s="127" t="n"/>
       <c r="B10" s="285" t="inlineStr">
         <is>
@@ -3687,9 +3699,10 @@
       </c>
       <c r="D10" s="258" t="inlineStr">
         <is>
-          <t>文章の執筆、LP構成、ステップメール設計、特典作成、配信設定、
-数値分析（開封率・クリック率）は私が担当いたします。
-〇〇様には、方向性のご確認と、最終的な配信・クロージングをお願いできればと思います。
+          <t>手順書・AIツール・テンプレート集の制作、初回レクチャーの実施、
+受講生への質問対応、実証データの記録と報告は、すべて私が担当いたします。
+〇〇様には、講座としての位置づけのご判断と、メンバーへの告知をお願いできればと存じます。
+既存のゼロイチ講座とは競合せず、note媒体に特化した後工程として設計しております。
 ご多忙中恐れ入りますが、ご検討いただけますと幸いです。</t>
         </is>
       </c>
@@ -4714,10 +4727,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C4:D4"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B8:B13"/>
-    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B5:B7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/_ JV攻略マイルストーン ワークシート.xlsx
+++ b/_ JV攻略マイルストーン ワークシート.xlsx
@@ -29,7 +29,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m\-d"/>
   </numFmts>
-  <fonts count="77">
+  <fonts count="78">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -482,6 +482,11 @@
       <color rgb="000000FF"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000000FF"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="37">
     <fill>
@@ -1481,7 +1486,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="364">
+  <cellXfs count="365">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2481,6 +2486,9 @@
     </xf>
     <xf numFmtId="0" fontId="46" fillId="6" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3752,7 +3760,11 @@
         </is>
       </c>
       <c r="C2" s="271" t="n"/>
-      <c r="D2" s="271" t="n"/>
+      <c r="D2" s="364" t="inlineStr">
+        <is>
+          <t>※ JV先は2層ある。第1層＝プレダイ運営（講師ポジション）／第2層＝実務パートナー（デザイン・ツール開発）。第2層はJV成立を前提とせず、自分で全工程を進めながら並行して探す。</t>
+        </is>
+      </c>
       <c r="E2" s="271" t="n"/>
       <c r="F2" s="271" t="n"/>
       <c r="G2" s="271" t="n"/>
@@ -3807,13 +3819,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="76.5" customHeight="1" s="272">
+    <row r="5" ht="100" customHeight="1" s="272">
       <c r="B5" s="250" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="263" t="inlineStr">
         <is>
-          <t>ホーリーさん</t>
+          <t>プレダイ運営（主催）</t>
         </is>
       </c>
       <c r="D5" s="263" t="inlineStr">
@@ -3823,198 +3835,284 @@
       </c>
       <c r="E5" s="263" t="inlineStr">
         <is>
-          <t>※未ヒアリング</t>
+          <t>ゼロイチ・スタート期のメンバーが本編に乗れず、EXルートで足踏みしている。
+note に特化した講座がラインナップにない。
+※ 直接ヒアリングできる関係ではないため、工程表の構造から推定。</t>
         </is>
       </c>
       <c r="F5" s="263" t="inlineStr">
         <is>
-          <t>教育〜販売の設計・構築（ステップメール6教育／LP4段構成）、
-特典作成、配信設定、数値分析、AIによる自動化。
-集客の裏側にある「売れる仕組み」を丸ごと担当できる。</t>
+          <t>note ゼロイチの手順書／note特化AIツール一式／Canvaテンプレート集／初回レクチャー。
+ゼロイチ層を次の段階へ進め、JV・サミットなど本編に乗せる。
+実証データ（達成率・所要日数・総作業時間）を開示する。</t>
         </is>
       </c>
       <c r="G5" s="263" t="inlineStr">
         <is>
-          <t>未定（Step4-5のオファー雛形をベースに作成する）</t>
+          <t>Step4-5 のオファー資料。
+※ 実証の数値が埋まるまで提出しない。</t>
         </is>
       </c>
       <c r="H5" s="263" t="inlineStr">
         <is>
-          <t>プレダイの同じチーム。一度Zoomで話したことがある。</t>
+          <t>主催から講師の道を示唆いただいており、運営も認識済み。営業は不要。</t>
         </is>
       </c>
       <c r="I5" s="263" t="inlineStr">
         <is>
-          <t>一度Zoomで会話済み。その後の接点はなし。
-まず関係づくりから再開する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="76.5" customHeight="1" s="272">
+          <t>示唆をいただいた段階。実証（段階0→3）を進行中。
+第2陣の結果が出た時点で Step4-5 を提出する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1" s="272">
       <c r="B6" s="251" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="264" t="inlineStr">
+      <c r="C6" s="263" t="inlineStr">
         <is>
           <t>YIさん</t>
         </is>
       </c>
-      <c r="D6" s="264" t="inlineStr">
+      <c r="D6" s="263" t="inlineStr">
         <is>
           <t>※要記入</t>
         </is>
       </c>
-      <c r="E6" s="264" t="inlineStr">
+      <c r="E6" s="263" t="inlineStr">
         <is>
           <t>商品はあるが、集客ができていない。</t>
         </is>
       </c>
-      <c r="F6" s="264" t="inlineStr">
-        <is>
-          <t>自分のリスト（メルマガ約300人／noteフォロワー約9,000人）への告知で集客を支援する。
-加えて教育〜販売の設計・構築（ステップメール／LP）とAI自動化。
-※どう支援するのが最適かは現在学習中。</t>
-        </is>
-      </c>
-      <c r="G6" s="264" t="inlineStr">
-        <is>
-          <t>未定（コンビとしての役割分担を前提に設計する）</t>
-        </is>
-      </c>
-      <c r="H6" s="264" t="inlineStr">
+      <c r="F6" s="263" t="inlineStr">
+        <is>
+          <t>【実務JV候補】AIツールの共同開発。
+ただし今回のレベルの内容を任せるのは難しいと判断。</t>
+        </is>
+      </c>
+      <c r="G6" s="263" t="inlineStr">
+        <is>
+          <t>未定。まず信頼関係の再構築から。</t>
+        </is>
+      </c>
+      <c r="H6" s="263" t="inlineStr">
         <is>
           <t>すでにコンビを組んでいる（既存の関係）</t>
         </is>
       </c>
-      <c r="I6" s="264" t="inlineStr">
-        <is>
-          <t>すでにコンビを組んでいる。
-YIさんの集客を、こちらのリストでどう支援できるかを学習中。
-現在はお互い動けていないが、状況が改善すれば一緒に動ける。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="12.75" customHeight="1" s="272">
+      <c r="I6" s="263" t="inlineStr">
+        <is>
+          <t>第2層（実務JV）の唯一の候補。ただし交渉・詳細説明のステップに相応の時間がかかり、
+確実性も低い。JVの成立を待たず、自分で全工程を進める方針。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="76" customHeight="1" s="272">
       <c r="B7" s="251" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="264" t="inlineStr">
-        <is>
-          <t>はるティさん</t>
-        </is>
-      </c>
-      <c r="D7" s="264" t="inlineStr">
-        <is>
-          <t>※要記入</t>
-        </is>
-      </c>
-      <c r="E7" s="264" t="inlineStr">
-        <is>
-          <t>※未ヒアリング（まずリサーチから）</t>
-        </is>
-      </c>
-      <c r="F7" s="264" t="inlineStr">
-        <is>
-          <t>教育〜販売の設計・構築（ステップメール6教育／LP4段構成）、
-特典作成、配信設定、数値分析、AIによる自動化。
-集客の裏側にある「売れる仕組み」を丸ごと担当できる。</t>
-        </is>
-      </c>
-      <c r="G7" s="264" t="inlineStr">
-        <is>
-          <t>未定（Step4-5のオファー雛形をベースに作成する）</t>
-        </is>
-      </c>
-      <c r="H7" s="264" t="inlineStr">
-        <is>
-          <t>現在リサーチ中。メルマガ・発信を追っている段階。</t>
-        </is>
-      </c>
-      <c r="I7" s="264" t="inlineStr">
-        <is>
-          <t>未接触。自分より遥か格上のため、
-まず裏方として渡せる実績を作ってから接触する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="12.75" customHeight="1" s="272">
+      <c r="C7" s="263" t="inlineStr">
+        <is>
+          <t>（未定）
+Canvaテンプレート
+制作パートナー</t>
+        </is>
+      </c>
+      <c r="D7" s="263" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="263" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="263" t="inlineStr">
+        <is>
+          <t>Canvaテンプレート集（固定記事・アカウントページのヘッダー用）の制作を依頼する。</t>
+        </is>
+      </c>
+      <c r="G7" s="263" t="inlineStr">
+        <is>
+          <t>一度きりの制作として依頼する。
+継続制作は相手の負担が読めず断られやすい。</t>
+        </is>
+      </c>
+      <c r="H7" s="263" t="inlineStr">
+        <is>
+          <t>未定。コミュニティ内・SNSで探す。</t>
+        </is>
+      </c>
+      <c r="I7" s="263" t="inlineStr">
+        <is>
+          <t>未着手。自作でも成立するため必須ではない。
+見つかれば着手が早まるという位置づけ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="62" customHeight="1" s="272">
       <c r="B8" s="251" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="264" t="inlineStr">
-        <is>
-          <t>くさばさん</t>
-        </is>
-      </c>
-      <c r="D8" s="264" t="inlineStr">
-        <is>
-          <t>※要記入</t>
-        </is>
-      </c>
-      <c r="E8" s="264" t="inlineStr">
-        <is>
-          <t>※未ヒアリング（まずリサーチから）</t>
-        </is>
-      </c>
-      <c r="F8" s="264" t="inlineStr">
-        <is>
-          <t>教育〜販売の設計・構築（ステップメール6教育／LP4段構成）、
-特典作成、配信設定、数値分析、AIによる自動化。
-集客の裏側にある「売れる仕組み」を丸ごと担当できる。</t>
-        </is>
-      </c>
-      <c r="G8" s="264" t="inlineStr">
-        <is>
-          <t>未定（Step4-5のオファー雛形をベースに作成する）</t>
-        </is>
-      </c>
-      <c r="H8" s="264" t="inlineStr">
-        <is>
-          <t>現在リサーチ中。メルマガ・発信を追っている段階。</t>
-        </is>
-      </c>
-      <c r="I8" s="264" t="inlineStr">
-        <is>
-          <t>未接触。自分より遥か格上のため、
-まず裏方として渡せる実績を作ってから接触する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="12.75" customHeight="1" s="272">
+      <c r="C8" s="263" t="inlineStr">
+        <is>
+          <t>（未定）
+AIツール
+共同開発パートナー</t>
+        </is>
+      </c>
+      <c r="D8" s="263" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="263" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="263" t="inlineStr">
+        <is>
+          <t>note特化AIツール（11点）の共同開発。</t>
+        </is>
+      </c>
+      <c r="G8" s="263" t="inlineStr">
+        <is>
+          <t>未定。</t>
+        </is>
+      </c>
+      <c r="H8" s="263" t="inlineStr">
+        <is>
+          <t>未定。コミュニティ内・SNSで探す。</t>
+        </is>
+      </c>
+      <c r="I8" s="263" t="inlineStr">
+        <is>
+          <t>未着手。自作可能なため必須ではない。速度を買う判断。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="62" customHeight="1" s="272">
       <c r="B9" s="251" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="252" t="n"/>
-      <c r="D9" s="252" t="n"/>
-      <c r="E9" s="252" t="n"/>
-      <c r="F9" s="252" t="n"/>
-      <c r="G9" s="252" t="n"/>
-      <c r="H9" s="252" t="n"/>
-      <c r="I9" s="252" t="n"/>
-    </row>
-    <row r="10" ht="12.75" customHeight="1" s="272">
+      <c r="C9" s="263" t="inlineStr">
+        <is>
+          <t>ホーリーさん</t>
+        </is>
+      </c>
+      <c r="D9" s="263" t="inlineStr">
+        <is>
+          <t>※要記入</t>
+        </is>
+      </c>
+      <c r="E9" s="263" t="inlineStr">
+        <is>
+          <t>※未ヒアリング</t>
+        </is>
+      </c>
+      <c r="F9" s="263" t="inlineStr">
+        <is>
+          <t>【保留】旧戦略（相手のリストを借りる）の候補だった。</t>
+        </is>
+      </c>
+      <c r="G9" s="263" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="263" t="inlineStr">
+        <is>
+          <t>プレダイの同じチーム。一度Zoomで話したことがある。</t>
+        </is>
+      </c>
+      <c r="I9" s="263" t="inlineStr">
+        <is>
+          <t>【保留】現在の講師ポジション路線では役割がない。
+同じコミュニティにいるため、関係は維持する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="50" customHeight="1" s="272">
       <c r="B10" s="251" t="n">
         <v>6</v>
       </c>
-      <c r="C10" s="252" t="n"/>
-      <c r="D10" s="252" t="n"/>
-      <c r="E10" s="252" t="n"/>
-      <c r="F10" s="252" t="n"/>
-      <c r="G10" s="252" t="n"/>
-      <c r="H10" s="252" t="n"/>
-      <c r="I10" s="252" t="n"/>
-    </row>
-    <row r="11" ht="12.75" customHeight="1" s="272">
+      <c r="C10" s="263" t="inlineStr">
+        <is>
+          <t>はるティさん</t>
+        </is>
+      </c>
+      <c r="D10" s="263" t="inlineStr">
+        <is>
+          <t>※要記入</t>
+        </is>
+      </c>
+      <c r="E10" s="263" t="inlineStr">
+        <is>
+          <t>※未ヒアリング</t>
+        </is>
+      </c>
+      <c r="F10" s="263" t="inlineStr">
+        <is>
+          <t>【保留】旧戦略の候補だった。格上のためリサーチ中だった。</t>
+        </is>
+      </c>
+      <c r="G10" s="263" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" s="263" t="inlineStr">
+        <is>
+          <t>未接触。</t>
+        </is>
+      </c>
+      <c r="I10" s="263" t="inlineStr">
+        <is>
+          <t>【保留】現路線では対象外。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="50" customHeight="1" s="272">
       <c r="B11" s="251" t="n">
         <v>7</v>
       </c>
-      <c r="C11" s="252" t="n"/>
-      <c r="D11" s="252" t="n"/>
-      <c r="E11" s="252" t="n"/>
-      <c r="F11" s="252" t="n"/>
-      <c r="G11" s="252" t="n"/>
-      <c r="H11" s="252" t="n"/>
-      <c r="I11" s="252" t="n"/>
+      <c r="C11" s="263" t="inlineStr">
+        <is>
+          <t>くさばさん</t>
+        </is>
+      </c>
+      <c r="D11" s="263" t="inlineStr">
+        <is>
+          <t>※要記入</t>
+        </is>
+      </c>
+      <c r="E11" s="263" t="inlineStr">
+        <is>
+          <t>※未ヒアリング</t>
+        </is>
+      </c>
+      <c r="F11" s="263" t="inlineStr">
+        <is>
+          <t>【保留】旧戦略の候補だった。格上のためリサーチ中だった。</t>
+        </is>
+      </c>
+      <c r="G11" s="263" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="263" t="inlineStr">
+        <is>
+          <t>未接触。</t>
+        </is>
+      </c>
+      <c r="I11" s="263" t="inlineStr">
+        <is>
+          <t>【保留】現路線では対象外。</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="12.75" customHeight="1" s="272">
       <c r="B12" s="251" t="n">
@@ -4727,10 +4825,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B8:B13"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B5:B7"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B8:B13"/>
-    <mergeCell ref="B5:B7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/_ JV攻略マイルストーン ワークシート.xlsx
+++ b/_ JV攻略マイルストーン ワークシート.xlsx
@@ -4825,9 +4825,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B2:D2"/>
     <mergeCell ref="B8:B13"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B5:B7"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="F4" s="127" t="n"/>
     </row>
-    <row r="5" ht="81.75" customHeight="1" s="272">
+    <row r="5" ht="108" customHeight="1" s="272">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="131" t="inlineStr">
         <is>
@@ -4924,16 +4924,19 @@
       </c>
       <c r="E5" s="258" t="inlineStr">
         <is>
-          <t>・note フォロワー 約9,000人
+          <t>・note フォロワー 約9,000人（メインアカウント）
+・note フォロワー 約900人（サブアカウント／検証用）
 ・メルマガ読者 約300人
 ・公式LINE／オープンチャット 約15人
 ・note購入者・メルマガ読者との信頼関係
-・文章だけで「人柄を信じて買います」と言われる関係性</t>
+・文章だけで「人柄を信じて買います」と言われる関係性
+※ プレダイのゼロイチ未達メンバーが受講生候補だが、
+　 これは自分の顧客資産ではなくコミュニティ側の資産。混同しない。</t>
         </is>
       </c>
       <c r="F5" s="127" t="n"/>
     </row>
-    <row r="6" ht="81.75" customHeight="1" s="272">
+    <row r="6" ht="100" customHeight="1" s="272">
       <c r="A6" s="127" t="n"/>
       <c r="B6" s="131" t="inlineStr">
         <is>
@@ -4961,7 +4964,9 @@
       </c>
       <c r="E6" s="268" t="inlineStr">
         <is>
-          <t>・看護師歴10年以上（訪問看護・幅広い診療科を経験）
+          <t>・プレダイ主催から note 講師の道を示唆されている（運営も認識済み・席は空いている）
+・サブアカウント（フォロワー900人強）で有料noteを販売し、5日で初売上を達成
+・看護師歴10年以上（訪問看護・幅広い診療科を経験）
 ・note発信の実績（フォロワー約9,000人）
 ・「無料でここまで体系化された情報は初めて」と言われる
 ・Kindle出版（進行中）
@@ -4970,7 +4975,7 @@
       </c>
       <c r="F6" s="127" t="n"/>
     </row>
-    <row r="7" ht="81.75" customHeight="1" s="272">
+    <row r="7" ht="100" customHeight="1" s="272">
       <c r="A7" s="127" t="n"/>
       <c r="B7" s="131" t="inlineStr">
         <is>
@@ -4996,16 +5001,18 @@
       </c>
       <c r="E7" s="258" t="inlineStr">
         <is>
-          <t>・note集客×メルマガ教育・販売の型（実践ベース）
+          <t>・有料note販売のノウハウ（自分の実証をもとに体系化）
+・note の仕組み構築方法（記事 → 導線 → 販売の組み立て）
+・note集客×メルマガ教育・販売の型（上位商品用）
 ・ステップメール6教育／LP4段構成のノウハウ
 ・セールスライティングの知識
-・自作AIツール10個以上（文章生成・LP作成・SNS自動投稿・QRコード生成・ファイル変換など）
-・自分の文体を学習させたAIライティング（型と自分らしさを両立）</t>
+・自分の文体を学習させたAIライティング（型と自分らしさを両立）
+・note ゼロイチ講座（開発中）</t>
         </is>
       </c>
       <c r="F7" s="127" t="n"/>
     </row>
-    <row r="8" ht="81.75" customHeight="1" s="272">
+    <row r="8" ht="108" customHeight="1" s="272">
       <c r="A8" s="127" t="n"/>
       <c r="B8" s="131" t="inlineStr">
         <is>
@@ -5032,16 +5039,19 @@
       </c>
       <c r="E8" s="258" t="inlineStr">
         <is>
-          <t>・自作の文章生成AI（自分の文体・知識ベース）
-・SNS自動投稿の仕組み
+          <t>・Claude Code ベースの自作AIツール10個以上
+・note特化のツール群（売れている有料記事のリサーチ／投稿の構成作り／
+　アカウント名・プロフィール・自己紹介文の作成／有料記事のセールス部分＋有料部分／
+　特典作成／毎日投稿の自動化）
+・自作の文章生成AI（自分の文体・知識ベース）
 ・LP作成／コンテンツ生成AIツール
 ・QRコード生成・ファイル変換などの補助ツール
-・note→メルマガ→販売の自動化導線</t>
+・Canva テンプレート集（固定記事・アカウントページのヘッダー用／制作予定）</t>
         </is>
       </c>
       <c r="F8" s="127" t="n"/>
     </row>
-    <row r="9" ht="81.75" customHeight="1" s="272">
+    <row r="9" ht="100" customHeight="1" s="272">
       <c r="A9" s="127" t="n"/>
       <c r="B9" s="131" t="inlineStr">
         <is>
@@ -5068,16 +5078,18 @@
       </c>
       <c r="E9" s="258" t="inlineStr">
         <is>
-          <t>・コンビを組む予定のコンテンツビジネス仲間（1人）
-・コンテンツビジネスの友人（もう1人）
+          <t>・プレダイのコミュニティ（主催・既存講師・メンバー）
+・コンビを組んでいるコンテンツビジネス仲間（YIさん）
+・ホーリーさん（プレダイ同チーム・Zoomで会話済み）
+・コンテンツビジネスの友人（1人）
 ・同僚のTikTokインフルエンサー
-・プレダイのコミュニティ
-※前コミュニティの繋がりは現在は絶縁</t>
+※ 前コミュニティの繋がりは現在は絶縁
+※ デザイン・ツール開発の実務パートナーは未開拓（Step5-1で管理）</t>
         </is>
       </c>
       <c r="F9" s="127" t="n"/>
     </row>
-    <row r="10" ht="81.75" customHeight="1" s="272">
+    <row r="10" ht="108" customHeight="1" s="272">
       <c r="A10" s="127" t="n"/>
       <c r="B10" s="131" t="inlineStr">
         <is>
@@ -5106,12 +5118,14 @@
       </c>
       <c r="E10" s="258" t="inlineStr">
         <is>
-          <t>・note（無料記事→固定記事→メルマガ登録）
-・メルマガ（教育・販売の主軸）
+          <t>・note（無料記事 → 固定記事 → 有料記事）※ ゼロイチ講座の主導線
+・note（無料記事 → 固定記事 → メルマガ登録）※ 上位商品の導線
+・メルマガ（教育・販売）
 ・Kindle（導線として活用）
 ・スタエフ（音声集客）
 ・X／SNS
-・公式LINE</t>
+・公式LINE
+※ プレダイのコミュニティは、講師として認められれば告知チャネルになる（現時点では未取得）</t>
         </is>
       </c>
       <c r="F10" s="127" t="n"/>

--- a/_ JV攻略マイルストーン ワークシート.xlsx
+++ b/_ JV攻略マイルストーン ワークシート.xlsx
@@ -2862,7 +2862,7 @@
         </is>
       </c>
       <c r="F5" s="18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1" t="n"/>
     </row>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="F8" s="31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1" t="n"/>
     </row>
@@ -2936,7 +2936,7 @@
         </is>
       </c>
       <c r="F9" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1" t="n"/>
     </row>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="F10" s="36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1" t="n"/>
     </row>
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="F13" s="46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="1" t="n"/>
     </row>
@@ -3050,7 +3050,7 @@
         </is>
       </c>
       <c r="F16" s="58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="1" t="n"/>
     </row>
@@ -3072,7 +3072,7 @@
         </is>
       </c>
       <c r="F17" s="63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="1" t="n"/>
     </row>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="F21" s="80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" s="68" t="n"/>
     </row>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="F22" s="80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" s="68" t="n"/>
     </row>
@@ -3214,7 +3214,7 @@
         </is>
       </c>
       <c r="F24" s="80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="68" t="n"/>
     </row>
@@ -3236,7 +3236,7 @@
         </is>
       </c>
       <c r="F25" s="88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="68" t="n"/>
     </row>
@@ -3258,7 +3258,7 @@
         </is>
       </c>
       <c r="F26" s="91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="68" t="n"/>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F27" s="95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" s="68" t="n"/>
     </row>
@@ -4825,10 +4825,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C4:D4"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B8:B13"/>
-    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B5:B7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/_ JV攻略マイルストーン ワークシート.xlsx
+++ b/_ JV攻略マイルストーン ワークシート.xlsx
@@ -3548,7 +3548,7 @@
       </c>
       <c r="E4" s="127" t="n"/>
     </row>
-    <row r="5" ht="90" customHeight="1" s="272">
+    <row r="5" ht="100" customHeight="1" s="272">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="285" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="E5" s="127" t="n"/>
     </row>
-    <row r="6" ht="110" customHeight="1" s="272">
+    <row r="6" ht="160" customHeight="1" s="272">
       <c r="A6" s="127" t="n"/>
       <c r="B6" s="285" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="E6" s="127" t="n"/>
     </row>
-    <row r="7" ht="118" customHeight="1" s="272">
+    <row r="7" ht="148" customHeight="1" s="272">
       <c r="A7" s="127" t="n"/>
       <c r="B7" s="285" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="E7" s="127" t="n"/>
     </row>
-    <row r="8" ht="110" customHeight="1" s="272">
+    <row r="8" ht="136" customHeight="1" s="272">
       <c r="A8" s="127" t="n"/>
       <c r="B8" s="285" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="E8" s="127" t="n"/>
     </row>
-    <row r="9" ht="100" customHeight="1" s="272">
+    <row r="9" ht="124" customHeight="1" s="272">
       <c r="A9" s="127" t="n"/>
       <c r="B9" s="285" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="E9" s="127" t="n"/>
     </row>
-    <row r="10" ht="90" customHeight="1" s="272">
+    <row r="10" ht="112" customHeight="1" s="272">
       <c r="A10" s="127" t="n"/>
       <c r="B10" s="285" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="100" customHeight="1" s="272">
+    <row r="5" ht="326" customHeight="1" s="272">
       <c r="B5" s="250" t="n">
         <v>1</v>
       </c>
@@ -3865,7 +3865,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="90" customHeight="1" s="272">
+    <row r="6" ht="151" customHeight="1" s="272">
       <c r="B6" s="251" t="n">
         <v>2</v>
       </c>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="76" customHeight="1" s="272">
+    <row r="7" ht="137" customHeight="1" s="272">
       <c r="B7" s="251" t="n">
         <v>3</v>
       </c>
@@ -3951,7 +3951,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="62" customHeight="1" s="272">
+    <row r="8" ht="70" customHeight="1" s="272">
       <c r="B8" s="251" t="n">
         <v>4</v>
       </c>
@@ -3993,7 +3993,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="62" customHeight="1" s="272">
+    <row r="9" ht="97" customHeight="1" s="272">
       <c r="B9" s="251" t="n">
         <v>5</v>
       </c>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="50" customHeight="1" s="272">
+    <row r="10" ht="97" customHeight="1" s="272">
       <c r="B10" s="251" t="n">
         <v>6</v>
       </c>
@@ -4074,7 +4074,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="50" customHeight="1" s="272">
+    <row r="11" ht="97" customHeight="1" s="272">
       <c r="B11" s="251" t="n">
         <v>7</v>
       </c>
@@ -4825,10 +4825,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B8:B13"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B5:B7"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B8:B13"/>
-    <mergeCell ref="B5:B7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="F4" s="127" t="n"/>
     </row>
-    <row r="5" ht="108" customHeight="1" s="272">
+    <row r="5" ht="160" customHeight="1" s="272">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="131" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="F5" s="127" t="n"/>
     </row>
-    <row r="6" ht="100" customHeight="1" s="272">
+    <row r="6" ht="160" customHeight="1" s="272">
       <c r="A6" s="127" t="n"/>
       <c r="B6" s="131" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="F6" s="127" t="n"/>
     </row>
-    <row r="7" ht="100" customHeight="1" s="272">
+    <row r="7" ht="148" customHeight="1" s="272">
       <c r="A7" s="127" t="n"/>
       <c r="B7" s="131" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="F7" s="127" t="n"/>
     </row>
-    <row r="8" ht="108" customHeight="1" s="272">
+    <row r="8" ht="185" customHeight="1" s="272">
       <c r="A8" s="127" t="n"/>
       <c r="B8" s="131" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="F8" s="127" t="n"/>
     </row>
-    <row r="9" ht="100" customHeight="1" s="272">
+    <row r="9" ht="136" customHeight="1" s="272">
       <c r="A9" s="127" t="n"/>
       <c r="B9" s="131" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="F9" s="127" t="n"/>
     </row>
-    <row r="10" ht="108" customHeight="1" s="272">
+    <row r="10" ht="148" customHeight="1" s="272">
       <c r="A10" s="127" t="n"/>
       <c r="B10" s="131" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="D13" s="127" t="n"/>
     </row>
-    <row r="14" ht="520" customHeight="1" s="272">
+    <row r="14" ht="637" customHeight="1" s="272">
       <c r="A14" s="127" t="n"/>
       <c r="B14" s="138" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1" s="272">
+    <row r="5" ht="440" customHeight="1" s="272">
       <c r="A5" s="141" t="n"/>
       <c r="B5" s="289" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="36" customHeight="1" s="272">
+    <row r="6" ht="185" customHeight="1" s="272">
       <c r="A6" s="141" t="n"/>
       <c r="B6" s="287" t="n"/>
       <c r="C6" s="285" t="inlineStr">
@@ -5481,7 +5481,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" s="272">
+    <row r="7" ht="148" customHeight="1" s="272">
       <c r="A7" s="141" t="n"/>
       <c r="B7" s="287" t="n"/>
       <c r="C7" s="285" t="inlineStr">
@@ -5502,7 +5502,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="48" customHeight="1" s="272">
+    <row r="8" ht="233" customHeight="1" s="272">
       <c r="A8" s="141" t="n"/>
       <c r="B8" s="287" t="n"/>
       <c r="C8" s="285" t="inlineStr">
@@ -5524,7 +5524,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="62" customHeight="1" s="272">
+    <row r="9" ht="306" customHeight="1" s="272">
       <c r="A9" s="141" t="n"/>
       <c r="B9" s="287" t="n"/>
       <c r="C9" s="285" t="inlineStr">
@@ -5547,7 +5547,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1" s="272">
+    <row r="10" ht="185" customHeight="1" s="272">
       <c r="A10" s="141" t="n"/>
       <c r="B10" s="287" t="n"/>
       <c r="C10" s="285" t="inlineStr">
@@ -5569,7 +5569,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="190" customHeight="1" s="272">
+    <row r="11" ht="987" customHeight="1" s="272">
       <c r="A11" s="141" t="n"/>
       <c r="B11" s="287" t="n"/>
       <c r="C11" s="285" t="inlineStr">
@@ -5604,7 +5604,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="132" customHeight="1" s="272">
+    <row r="12" ht="525" customHeight="1" s="272">
       <c r="A12" s="141" t="n"/>
       <c r="B12" s="287" t="n"/>
       <c r="C12" s="285" t="inlineStr">
@@ -5633,7 +5633,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="36" customHeight="1" s="272">
+    <row r="13" ht="160" customHeight="1" s="272">
       <c r="A13" s="141" t="n"/>
       <c r="B13" s="290" t="n"/>
       <c r="C13" s="288" t="inlineStr">
@@ -5654,7 +5654,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="272">
+    <row r="14" ht="63" customHeight="1" s="272">
       <c r="A14" s="144" t="n"/>
       <c r="B14" s="286" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="48" customHeight="1" s="272">
+    <row r="15" ht="51" customHeight="1" s="272">
       <c r="A15" s="144" t="n"/>
       <c r="B15" s="287" t="n"/>
       <c r="C15" s="285" t="inlineStr">
@@ -5701,7 +5701,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="40" customHeight="1" s="272">
+    <row r="16" ht="233" customHeight="1" s="272">
       <c r="A16" s="144" t="n"/>
       <c r="B16" s="287" t="n"/>
       <c r="C16" s="285" t="inlineStr">
@@ -5723,7 +5723,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="76" customHeight="1" s="272">
+    <row r="17" ht="416" customHeight="1" s="272">
       <c r="A17" s="144" t="n"/>
       <c r="B17" s="287" t="n"/>
       <c r="C17" s="285" t="inlineStr">
@@ -5750,7 +5750,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="84" customHeight="1" s="272">
+    <row r="18" ht="355" customHeight="1" s="272">
       <c r="A18" s="144" t="n"/>
       <c r="B18" s="287" t="n"/>
       <c r="C18" s="285" t="inlineStr">
@@ -5779,7 +5779,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="84" customHeight="1" s="272">
+    <row r="19" ht="294" customHeight="1" s="272">
       <c r="A19" s="144" t="n"/>
       <c r="B19" s="287" t="n"/>
       <c r="C19" s="285" t="inlineStr">
@@ -5807,7 +5807,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="272">
+    <row r="20" ht="27" customHeight="1" s="272">
       <c r="A20" s="144" t="n"/>
       <c r="B20" s="287" t="n"/>
       <c r="C20" s="285" t="inlineStr">
@@ -5827,7 +5827,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="272">
+    <row r="21" ht="51" customHeight="1" s="272">
       <c r="A21" s="144" t="n"/>
       <c r="B21" s="287" t="n"/>
       <c r="C21" s="285" t="inlineStr">
@@ -5847,7 +5847,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="24" customHeight="1" s="272">
+    <row r="22" ht="39" customHeight="1" s="272">
       <c r="A22" s="144" t="n"/>
       <c r="B22" s="287" t="n"/>
       <c r="C22" s="285" t="inlineStr">
@@ -5867,7 +5867,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1" s="272">
+    <row r="23" ht="124" customHeight="1" s="272">
       <c r="A23" s="144" t="n"/>
       <c r="B23" s="287" t="n"/>
       <c r="C23" s="285" t="inlineStr">
@@ -5891,7 +5891,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1" s="272">
+    <row r="24" ht="160" customHeight="1" s="272">
       <c r="A24" s="144" t="n"/>
       <c r="B24" s="287" t="n"/>
       <c r="C24" s="277" t="n"/>
@@ -5912,7 +5912,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1" s="272">
+    <row r="25" ht="112" customHeight="1" s="272">
       <c r="A25" s="144" t="n"/>
       <c r="B25" s="287" t="n"/>
       <c r="C25" s="285" t="inlineStr">
@@ -5936,7 +5936,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="272">
+    <row r="26" ht="100" customHeight="1" s="272">
       <c r="A26" s="144" t="n"/>
       <c r="B26" s="287" t="n"/>
       <c r="C26" s="277" t="n"/>
@@ -5956,7 +5956,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="272">
+    <row r="27" ht="39" customHeight="1" s="272">
       <c r="A27" s="144" t="n"/>
       <c r="B27" s="287" t="n"/>
       <c r="C27" s="285" t="inlineStr">
@@ -5980,7 +5980,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="272">
+    <row r="28" ht="63" customHeight="1" s="272">
       <c r="A28" s="144" t="n"/>
       <c r="B28" s="287" t="n"/>
       <c r="C28" s="277" t="n"/>
@@ -6000,7 +6000,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="48" customHeight="1" s="272">
+    <row r="29" ht="112" customHeight="1" s="272">
       <c r="A29" s="144" t="n"/>
       <c r="B29" s="287" t="n"/>
       <c r="C29" s="285" t="inlineStr">
@@ -6023,7 +6023,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1" s="272">
+    <row r="30" ht="112" customHeight="1" s="272">
       <c r="A30" s="144" t="n"/>
       <c r="B30" s="287" t="n"/>
       <c r="C30" s="285" t="inlineStr">
@@ -6043,7 +6043,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="272">
+    <row r="31" ht="63" customHeight="1" s="272">
       <c r="A31" s="144" t="n"/>
       <c r="B31" s="287" t="n"/>
       <c r="C31" s="285" t="inlineStr">
@@ -6063,7 +6063,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="36" customHeight="1" s="272">
+    <row r="32" ht="100" customHeight="1" s="272">
       <c r="A32" s="144" t="n"/>
       <c r="B32" s="287" t="n"/>
       <c r="C32" s="285" t="inlineStr">
@@ -6085,7 +6085,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1" s="272">
+    <row r="33" ht="112" customHeight="1" s="272">
       <c r="A33" s="144" t="n"/>
       <c r="B33" s="287" t="n"/>
       <c r="C33" s="285" t="inlineStr">
@@ -6107,7 +6107,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="272">
+    <row r="34" ht="39" customHeight="1" s="272">
       <c r="A34" s="144" t="n"/>
       <c r="B34" s="287" t="n"/>
       <c r="C34" s="285" t="inlineStr">
@@ -6127,7 +6127,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="48" customHeight="1" s="272">
+    <row r="35" ht="221" customHeight="1" s="272">
       <c r="A35" s="144" t="n"/>
       <c r="B35" s="287" t="n"/>
       <c r="C35" s="285" t="inlineStr">
@@ -6150,7 +6150,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="36" customHeight="1" s="272">
+    <row r="36" ht="136" customHeight="1" s="272">
       <c r="A36" s="144" t="n"/>
       <c r="B36" s="277" t="n"/>
       <c r="C36" s="285" t="inlineStr">
@@ -6265,7 +6265,7 @@
       <c r="A5" s="139" t="n"/>
       <c r="B5" s="149" t="n"/>
     </row>
-    <row r="6" ht="34" customHeight="1" s="272">
+    <row r="6" ht="259" customHeight="1" s="272">
       <c r="A6" s="139" t="n"/>
       <c r="B6" s="150" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="45" customHeight="1" s="272">
+    <row r="28" ht="51" customHeight="1" s="272">
       <c r="A28" s="159" t="n"/>
       <c r="B28" s="297" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="34" customHeight="1" s="272">
+    <row r="29" ht="35" customHeight="1" s="272">
       <c r="A29" s="159" t="n"/>
       <c r="B29" s="287" t="n"/>
       <c r="C29" s="287" t="n"/>
@@ -6682,7 +6682,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="34" customHeight="1" s="272">
+    <row r="30" ht="35" customHeight="1" s="272">
       <c r="A30" s="159" t="n"/>
       <c r="B30" s="277" t="n"/>
       <c r="C30" s="277" t="n"/>
@@ -6697,7 +6697,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="45" customHeight="1" s="272">
+    <row r="31" ht="46" customHeight="1" s="272">
       <c r="A31" s="159" t="n"/>
       <c r="B31" s="297" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="34" customHeight="1" s="272">
+    <row r="32" ht="51" customHeight="1" s="272">
       <c r="A32" s="159" t="n"/>
       <c r="B32" s="287" t="n"/>
       <c r="C32" s="287" t="n"/>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="34" customHeight="1" s="272">
+    <row r="33" ht="35" customHeight="1" s="272">
       <c r="A33" s="159" t="n"/>
       <c r="B33" s="277" t="n"/>
       <c r="C33" s="277" t="n"/>
@@ -6781,7 +6781,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="30" customHeight="1" s="272">
+    <row r="35" ht="51" customHeight="1" s="272">
       <c r="A35" s="159" t="n"/>
       <c r="B35" s="287" t="n"/>
       <c r="C35" s="287" t="n"/>
@@ -6796,7 +6796,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="34" customHeight="1" s="272">
+    <row r="36" ht="51" customHeight="1" s="272">
       <c r="A36" s="159" t="n"/>
       <c r="B36" s="277" t="n"/>
       <c r="C36" s="277" t="n"/>
@@ -6811,7 +6811,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="45" customHeight="1" s="272">
+    <row r="37" ht="51" customHeight="1" s="272">
       <c r="A37" s="159" t="n"/>
       <c r="B37" s="297" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="34" customHeight="1" s="272">
+    <row r="38" ht="35" customHeight="1" s="272">
       <c r="A38" s="159" t="n"/>
       <c r="B38" s="287" t="n"/>
       <c r="C38" s="287" t="n"/>
@@ -6851,7 +6851,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="34" customHeight="1" s="272">
+    <row r="39" ht="35" customHeight="1" s="272">
       <c r="A39" s="159" t="n"/>
       <c r="B39" s="277" t="n"/>
       <c r="C39" s="277" t="n"/>
@@ -6866,7 +6866,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="45" customHeight="1" s="272">
+    <row r="40" ht="51" customHeight="1" s="272">
       <c r="A40" s="159" t="n"/>
       <c r="B40" s="297" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="34" customHeight="1" s="272">
+    <row r="41" ht="35" customHeight="1" s="272">
       <c r="A41" s="159" t="n"/>
       <c r="B41" s="287" t="n"/>
       <c r="C41" s="287" t="n"/>
@@ -6906,7 +6906,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="34" customHeight="1" s="272">
+    <row r="42" ht="51" customHeight="1" s="272">
       <c r="A42" s="159" t="n"/>
       <c r="B42" s="277" t="n"/>
       <c r="C42" s="277" t="n"/>
@@ -7263,11 +7263,12 @@
       <c r="D22" s="181" t="n"/>
       <c r="E22" s="318" t="n"/>
     </row>
-    <row r="23" ht="13" customHeight="1" s="272">
+    <row r="23" ht="29" customHeight="1" s="272">
       <c r="B23" s="277" t="n"/>
       <c r="C23" s="182" t="inlineStr">
         <is>
-          <t>＜ ゼロイチで止まり、最初の1円が作れないという課題 ＞</t>
+          <t>＜ ゼロイチで止まり、
+　 最初の1円が作れないという課題 ＞</t>
         </is>
       </c>
       <c r="D23" s="183" t="inlineStr">
@@ -7277,7 +7278,7 @@
       </c>
       <c r="E23" s="318" t="n"/>
     </row>
-    <row r="24" ht="13" customHeight="1" s="272">
+    <row r="24" ht="29" customHeight="1" s="272">
       <c r="B24" s="285" t="inlineStr">
         <is>
           <t xml:space="preserve"> ❷ 対象客</t>
@@ -7285,7 +7286,8 @@
       </c>
       <c r="C24" s="184" t="inlineStr">
         <is>
-          <t>＜ プレダイのメンバーのうち、まだ売上が0円のゼロイチ未達層 ＞</t>
+          <t>＜ プレダイのメンバーのうち、
+　 まだ売上が0円のゼロイチ未達層 ＞</t>
         </is>
       </c>
       <c r="D24" s="185" t="inlineStr">
@@ -7295,7 +7297,7 @@
       </c>
       <c r="E24" s="318" t="n"/>
     </row>
-    <row r="25" ht="13" customHeight="1" s="272">
+    <row r="25" ht="43" customHeight="1" s="272">
       <c r="B25" s="285" t="inlineStr">
         <is>
           <t xml:space="preserve"> ❸ 商品・サービス名</t>
@@ -7303,7 +7305,8 @@
       </c>
       <c r="C25" s="184" t="inlineStr">
         <is>
-          <t>＜ note ゼロイチ講座（note特化のAIツール一式＋レクチャー付き） ＞</t>
+          <t>＜ note ゼロイチ講座
+　 （note特化のAIツール一式＋レクチャー付き） ＞</t>
         </is>
       </c>
       <c r="D25" s="185" t="inlineStr">
@@ -7313,7 +7316,7 @@
       </c>
       <c r="E25" s="318" t="n"/>
     </row>
-    <row r="26" ht="13" customHeight="1" s="272">
+    <row r="26" ht="16" customHeight="1" s="272">
       <c r="B26" s="285" t="inlineStr">
         <is>
           <t xml:space="preserve"> ❹ 商品・サービスのカテゴリ</t>
@@ -7345,11 +7348,12 @@
       <c r="D27" s="187" t="n"/>
       <c r="E27" s="318" t="n"/>
     </row>
-    <row r="28" ht="13" customHeight="1" s="272">
+    <row r="28" ht="29" customHeight="1" s="272">
       <c r="B28" s="277" t="n"/>
       <c r="C28" s="182" t="inlineStr">
         <is>
-          <t>＜ 実績もフォロワーもゼロの状態から、最初の1円を自分の手で作ること ＞</t>
+          <t>＜ 実績もフォロワーもゼロの状態から、
+　 最初の1円を自分の手で作ること ＞</t>
         </is>
       </c>
       <c r="D28" s="183" t="inlineStr">
@@ -7359,7 +7363,7 @@
       </c>
       <c r="E28" s="318" t="n"/>
     </row>
-    <row r="29" ht="13" customHeight="1" s="272">
+    <row r="29" ht="29" customHeight="1" s="272">
       <c r="B29" s="285" t="inlineStr">
         <is>
           <t xml:space="preserve"> ❻ 大半のユーザーの頭にある商品・サービス</t>
@@ -7367,7 +7371,8 @@
       </c>
       <c r="C29" s="184" t="inlineStr">
         <is>
-          <t>＜ 自己流のnote運用や、媒体を限定しない一般的なゼロイチ講座 ＞</t>
+          <t>＜ 自己流のnote運用や、
+　 媒体を限定しない一般的なゼロイチ講座 ＞</t>
         </is>
       </c>
       <c r="D29" s="185" t="inlineStr">
@@ -7377,7 +7382,7 @@
       </c>
       <c r="E29" s="318" t="n"/>
     </row>
-    <row r="30" ht="28" customHeight="1" s="272">
+    <row r="30" ht="70" customHeight="1" s="272">
       <c r="B30" s="288" t="inlineStr">
         <is>
           <t xml:space="preserve"> ❼ 差別化の決定的な特徴</t>
@@ -7385,8 +7390,10 @@
       </c>
       <c r="C30" s="188" t="inlineStr">
         <is>
-          <t>＜ note に特化したAIツール一式で、リサーチからアカウント設計、
-　 記事・特典の作成までを肩代わりし、少ない作業時間で最初の1円に到達できること ＞</t>
+          <t>＜ note に特化したAIツール一式で、
+　 リサーチからアカウント設計、
+　 記事・特典の作成までを肩代わりし、
+　 少ない作業時間で最初の1円に到達できること ＞</t>
         </is>
       </c>
       <c r="D30" s="189" t="inlineStr">
@@ -7410,11 +7417,12 @@
       <c r="D31" s="190" t="n"/>
       <c r="E31" s="318" t="n"/>
     </row>
-    <row r="32" ht="13" customHeight="1" s="272">
+    <row r="32" ht="29" customHeight="1" s="272">
       <c r="B32" s="277" t="n"/>
       <c r="C32" s="182" t="inlineStr">
         <is>
-          <t>＜ note という具体的な媒体に特化した講座 ＞</t>
+          <t>＜ note という具体的な
+　 媒体に特化した講座 ＞</t>
         </is>
       </c>
       <c r="D32" s="183" t="inlineStr">
@@ -7438,12 +7446,13 @@
       <c r="D33" s="187" t="n"/>
       <c r="E33" s="318" t="n"/>
     </row>
-    <row r="34" ht="28" customHeight="1" s="272">
+    <row r="34" ht="56" customHeight="1" s="272">
       <c r="B34" s="277" t="n"/>
       <c r="C34" s="182" t="inlineStr">
         <is>
-          <t>＜ ゼロイチで止まっていたメンバーが次の段階へ進み、
-　 コミュニティの本編（JV・サミット等）に乗れるようになります ＞</t>
+          <t>＜ ゼロイチで止まっていたメンバーが
+　 次の段階へ進み、コミュニティの本編
+　 （JV・サミット等）に乗れるようになります ＞</t>
         </is>
       </c>
       <c r="D34" s="183" t="inlineStr">
@@ -9340,14 +9349,14 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="12.75" customHeight="1" s="272">
+    <row r="17" ht="15" customHeight="1" s="272">
       <c r="B17" s="261" t="inlineStr">
         <is>
           <t>いきなり連絡してくる人（前触れも接点もなく本題から入る人）</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="12.75" customHeight="1" s="272">
+    <row r="18" ht="15" customHeight="1" s="272">
       <c r="B18" s="261" t="inlineStr">
         <is>
           <t>何を目的に連絡したのかを自ら明かさない人</t>
@@ -9428,7 +9437,7 @@
       <c r="R2" s="127" t="n"/>
       <c r="S2" s="127" t="n"/>
     </row>
-    <row r="3" ht="26" customHeight="1" s="272">
+    <row r="3" ht="88" customHeight="1" s="272">
       <c r="A3" s="127" t="n"/>
       <c r="B3" s="362" t="inlineStr">
         <is>
@@ -9543,7 +9552,7 @@
       </c>
       <c r="O5" s="127" t="n"/>
     </row>
-    <row r="6" ht="127.5" customHeight="1" s="272">
+    <row r="6" ht="137" customHeight="1" s="272">
       <c r="A6" s="127" t="n"/>
       <c r="C6" s="336" t="inlineStr">
         <is>
@@ -9635,7 +9644,7 @@
       <c r="N10" s="245" t="n"/>
       <c r="O10" s="127" t="n"/>
     </row>
-    <row r="11" ht="25.5" customHeight="1" s="272">
+    <row r="11" ht="124" customHeight="1" s="272">
       <c r="A11" s="127" t="n"/>
       <c r="C11" s="336" t="inlineStr">
         <is>
@@ -9726,7 +9735,7 @@
       <c r="N15" s="245" t="n"/>
       <c r="O15" s="127" t="n"/>
     </row>
-    <row r="16" ht="20" customHeight="1" s="272">
+    <row r="16" ht="178" customHeight="1" s="272">
       <c r="A16" s="127" t="n"/>
       <c r="C16" s="336" t="inlineStr">
         <is>
@@ -9818,7 +9827,7 @@
       <c r="N20" s="245" t="n"/>
       <c r="O20" s="127" t="n"/>
     </row>
-    <row r="21" ht="20" customHeight="1" s="272">
+    <row r="21" ht="124" customHeight="1" s="272">
       <c r="A21" s="127" t="n"/>
       <c r="C21" s="336" t="inlineStr">
         <is>
@@ -9909,7 +9918,7 @@
       <c r="N25" s="245" t="n"/>
       <c r="O25" s="127" t="n"/>
     </row>
-    <row r="26" ht="20" customHeight="1" s="272">
+    <row r="26" ht="124" customHeight="1" s="272">
       <c r="A26" s="127" t="n"/>
       <c r="C26" s="337" t="inlineStr">
         <is>
@@ -10131,7 +10140,7 @@
       </c>
       <c r="R33" s="127" t="n"/>
     </row>
-    <row r="34" ht="20" customHeight="1" s="272">
+    <row r="34" ht="164" customHeight="1" s="272">
       <c r="A34" s="127" t="n"/>
       <c r="C34" s="336" t="inlineStr">
         <is>
@@ -10237,7 +10246,7 @@
       <c r="Q38" s="245" t="n"/>
       <c r="R38" s="127" t="n"/>
     </row>
-    <row r="39" ht="20" customHeight="1" s="272">
+    <row r="39" ht="164" customHeight="1" s="272">
       <c r="A39" s="127" t="n"/>
       <c r="C39" s="336" t="inlineStr">
         <is>
@@ -10344,7 +10353,7 @@
       <c r="Q43" s="245" t="n"/>
       <c r="R43" s="127" t="n"/>
     </row>
-    <row r="44" ht="20" customHeight="1" s="272">
+    <row r="44" ht="137" customHeight="1" s="272">
       <c r="A44" s="127" t="n"/>
       <c r="C44" s="337" t="inlineStr">
         <is>

--- a/_ JV攻略マイルストーン ワークシート.xlsx
+++ b/_ JV攻略マイルストーン ワークシート.xlsx
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="F23" s="80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="68" t="n"/>
     </row>
@@ -4825,10 +4825,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B2:D2"/>
     <mergeCell ref="B8:B13"/>
-    <mergeCell ref="B2:D2"/>
     <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C4:D4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7822,9 +7822,14 @@
       <c r="D24" s="214" t="n"/>
       <c r="E24" s="327" t="n"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1" s="272">
+    <row r="25" ht="29" customHeight="1" s="272">
       <c r="B25" s="279" t="n"/>
-      <c r="C25" s="215" t="n"/>
+      <c r="C25" s="215" t="inlineStr">
+        <is>
+          <t>＜ ゼロイチ・スタート期の方が本編に進めず、
+　 EXルートで足踏みしているお悩み ＞</t>
+        </is>
+      </c>
       <c r="D25" s="216" t="inlineStr">
         <is>
           <t>の解消です。</t>
@@ -7832,13 +7837,18 @@
       </c>
       <c r="E25" s="277" t="n"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1" s="272">
+    <row r="26" ht="43" customHeight="1" s="272">
       <c r="B26" s="333" t="inlineStr">
         <is>
           <t xml:space="preserve"> ❷ 役に立てる相手（JVしたい人の属性）</t>
         </is>
       </c>
-      <c r="C26" s="217" t="n"/>
+      <c r="C26" s="217" t="inlineStr">
+        <is>
+          <t>＜ ゼロイチ層を先に進めたいが、
+　 note という媒体の講座までは手が回っていない運営 ＞</t>
+        </is>
+      </c>
       <c r="D26" s="218" t="inlineStr">
         <is>
           <t>の方向けに、</t>
@@ -7846,13 +7856,18 @@
       </c>
       <c r="E26" s="327" t="n"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1" s="272">
+    <row r="27" ht="29" customHeight="1" s="272">
       <c r="B27" s="333" t="inlineStr">
         <is>
           <t xml:space="preserve"> ❸ 手伝えること（無料ギブの中身）</t>
         </is>
       </c>
-      <c r="C27" s="220" t="n"/>
+      <c r="C27" s="220" t="inlineStr">
+        <is>
+          <t>＜ note でゼロイチを達成させる講座を、
+　 私が自費で作って実証すること ＞</t>
+        </is>
+      </c>
       <c r="D27" s="221" t="inlineStr">
         <is>
           <t>という、</t>
@@ -7860,13 +7875,17 @@
       </c>
       <c r="E27" s="327" t="n"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1" s="272">
+    <row r="28" ht="16" customHeight="1" s="272">
       <c r="B28" s="333" t="inlineStr">
         <is>
           <t xml:space="preserve"> ❹ そのお手伝いのカテゴリ</t>
         </is>
       </c>
-      <c r="C28" s="215" t="n"/>
+      <c r="C28" s="215" t="inlineStr">
+        <is>
+          <t>＜ note × AI によるゼロイチ支援 ＞</t>
+        </is>
+      </c>
       <c r="D28" s="216" t="inlineStr">
         <is>
           <t>ができます。</t>
@@ -7888,9 +7907,14 @@
       <c r="D29" s="223" t="n"/>
       <c r="E29" s="327" t="n"/>
     </row>
-    <row r="30" ht="27" customHeight="1" s="272">
+    <row r="30" ht="43" customHeight="1" s="272">
       <c r="B30" s="279" t="n"/>
-      <c r="C30" s="224" t="n"/>
+      <c r="C30" s="224" t="inlineStr">
+        <is>
+          <t>＜ ゼロイチで止まっていたメンバーが最初の1円を作り、
+　 JV・サミットなど本編に進めるようになります ＞</t>
+        </is>
+      </c>
       <c r="D30" s="225" t="inlineStr">
         <is>
           <t>。</t>
@@ -7898,13 +7922,18 @@
       </c>
       <c r="E30" s="277" t="n"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1" s="272">
+    <row r="31" ht="29" customHeight="1" s="272">
       <c r="B31" s="333" t="inlineStr">
         <is>
           <t xml:space="preserve"> ❻ 相手の“いつものやり方”（外注／自力／放置）</t>
         </is>
       </c>
-      <c r="C31" s="217" t="n"/>
+      <c r="C31" s="217" t="inlineStr">
+        <is>
+          <t>＜ 既存のゼロイチ講座での底上げや、
+　 メンバー各自の自己流の発信 ＞</t>
+        </is>
+      </c>
       <c r="D31" s="218" t="inlineStr">
         <is>
           <t>とは違って、</t>
@@ -7912,13 +7941,20 @@
       </c>
       <c r="E31" s="327" t="n"/>
     </row>
-    <row r="32" ht="39.75" customHeight="1" s="272">
+    <row r="32" ht="97" customHeight="1" s="272">
       <c r="B32" s="207" t="inlineStr">
         <is>
           <t xml:space="preserve"> ❼ あなたならではの強み（差別化）</t>
         </is>
       </c>
-      <c r="C32" s="226" t="n"/>
+      <c r="C32" s="226" t="inlineStr">
+        <is>
+          <t>＜ 私自身がコミュニティのメンバーで同じ教材を通ってきたので、
+　 ゼロイチ層がどこで詰まるかを内側から分かっていること。
+　 加えて note 特化のAIツール一式を自作しているため、
+　 費用ゼロで用意できます ＞</t>
+        </is>
+      </c>
       <c r="D32" s="227" t="inlineStr">
         <is>
           <t>という強みがあります。</t>
@@ -7940,9 +7976,14 @@
       <c r="D33" s="214" t="n"/>
       <c r="E33" s="335" t="n"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1" s="272">
+    <row r="34" ht="29" customHeight="1" s="272">
       <c r="B34" s="279" t="n"/>
-      <c r="C34" s="224" t="n"/>
+      <c r="C34" s="224" t="inlineStr">
+        <is>
+          <t>＜ 費用もリスクも一切かけず、
+　 まず個別ルートで3名だけ ＞</t>
+        </is>
+      </c>
       <c r="D34" s="229" t="inlineStr">
         <is>
           <t>お試しいただけて、</t>
@@ -7964,9 +8005,13 @@
       <c r="D35" s="223" t="n"/>
       <c r="E35" s="327" t="n"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1" s="272">
+    <row r="36" ht="29" customHeight="1" s="272">
       <c r="B36" s="279" t="n"/>
-      <c r="C36" s="224" t="n"/>
+      <c r="C36" s="224" t="inlineStr">
+        <is>
+          <t>＜ 追加コスト0で、ゼロイチ層を本編に送り込む導線が1本増えます ＞</t>
+        </is>
+      </c>
       <c r="D36" s="229" t="inlineStr">
         <is>
           <t>。</t>
@@ -7988,9 +8033,16 @@
       <c r="D37" s="214" t="n"/>
       <c r="E37" s="330" t="n"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1" s="272">
+    <row r="38" ht="83" customHeight="1" s="272">
       <c r="B38" s="279" t="n"/>
-      <c r="C38" s="224" t="n"/>
+      <c r="C38" s="224" t="inlineStr">
+        <is>
+          <t>＜ 私はいま実績を積んでいる段階です。
+　 まずは実証の結果をご報告させてください。
+　 成果を実感いただけたら、講師として担当させていただく
+　 ご相談ができれば嬉しいです ＞</t>
+        </is>
+      </c>
       <c r="D38" s="229" t="n"/>
       <c r="E38" s="293" t="n"/>
     </row>
